--- a/research/traditional_assets/database/data/spain/spain_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_restaurant_dining.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1003918292511212</v>
+        <v>0.1001745996779933</v>
       </c>
       <c r="C2">
-        <v>2532.243459138112</v>
+        <v>2514.518783812591</v>
       </c>
       <c r="D2">
-        <v>2356.243459138112</v>
+        <v>2365.656783812591</v>
       </c>
       <c r="E2">
-        <v>-1737.6</v>
+        <v>-1710.462</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27.138</v>
       </c>
       <c r="G2">
         <v>176</v>
@@ -1451,28 +1451,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3650414</v>
       </c>
       <c r="N2">
-        <v>349.1249999999999</v>
+        <v>347.7599585999999</v>
       </c>
       <c r="O2">
-        <v>87.28124999999999</v>
+        <v>86.93998964999999</v>
       </c>
       <c r="P2">
-        <v>261.8437499999999</v>
+        <v>260.81996895</v>
       </c>
       <c r="Q2">
-        <v>273.8437499999999</v>
+        <v>272.81996895</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1003918292511212</v>
+        <v>0.1008054037151448</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8509161016586271</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>255.7614736080532</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1001745996779933</v>
+        <v>0.09995737010486555</v>
       </c>
       <c r="C3">
-        <v>2514.518783812591</v>
+        <v>2496.869623693837</v>
       </c>
       <c r="D3">
-        <v>2365.656783812591</v>
+        <v>2375.145623693837</v>
       </c>
       <c r="E3">
-        <v>-1710.462</v>
+        <v>-1683.324</v>
       </c>
       <c r="F3">
-        <v>27.138</v>
+        <v>54.276</v>
       </c>
       <c r="G3">
         <v>176</v>
@@ -1533,28 +1533,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M3">
-        <v>1.3650414</v>
+        <v>2.7300828</v>
       </c>
       <c r="N3">
-        <v>347.7599585999999</v>
+        <v>346.3949172</v>
       </c>
       <c r="O3">
-        <v>86.93998964999999</v>
+        <v>86.59872929999999</v>
       </c>
       <c r="P3">
-        <v>260.81996895</v>
+        <v>259.7961878999999</v>
       </c>
       <c r="Q3">
-        <v>272.81996895</v>
+        <v>271.7961878999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1008054037151448</v>
+        <v>0.1012274184743526</v>
       </c>
       <c r="T3">
-        <v>0.8509161016586271</v>
+        <v>0.8574445357667952</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>255.7614736080532</v>
+        <v>127.8807368040266</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09995737010486555</v>
+        <v>0.09974014053173774</v>
       </c>
       <c r="C4">
-        <v>2496.869623693837</v>
+        <v>2479.296891134099</v>
       </c>
       <c r="D4">
-        <v>2375.145623693837</v>
+        <v>2384.710891134099</v>
       </c>
       <c r="E4">
-        <v>-1683.324</v>
+        <v>-1656.186</v>
       </c>
       <c r="F4">
-        <v>54.276</v>
+        <v>81.414</v>
       </c>
       <c r="G4">
         <v>176</v>
@@ -1615,28 +1615,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M4">
-        <v>2.7300828</v>
+        <v>4.0951242</v>
       </c>
       <c r="N4">
-        <v>346.3949172</v>
+        <v>345.0298758</v>
       </c>
       <c r="O4">
-        <v>86.59872929999999</v>
+        <v>86.25746894999999</v>
       </c>
       <c r="P4">
-        <v>259.7961878999999</v>
+        <v>258.77240685</v>
       </c>
       <c r="Q4">
-        <v>271.7961878999999</v>
+        <v>270.77240685</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1012274184743526</v>
+        <v>0.1016581345688018</v>
       </c>
       <c r="T4">
-        <v>0.8574445357667952</v>
+        <v>0.8641075767637914</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>127.8807368040266</v>
+        <v>85.25382453601773</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09974014053173774</v>
+        <v>0.09952291095860995</v>
       </c>
       <c r="C5">
-        <v>2479.296891134099</v>
+        <v>2461.801513242074</v>
       </c>
       <c r="D5">
-        <v>2384.710891134099</v>
+        <v>2394.353513242074</v>
       </c>
       <c r="E5">
-        <v>-1656.186</v>
+        <v>-1629.048</v>
       </c>
       <c r="F5">
-        <v>81.414</v>
+        <v>108.552</v>
       </c>
       <c r="G5">
         <v>176</v>
@@ -1697,28 +1697,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M5">
-        <v>4.0951242</v>
+        <v>5.4601656</v>
       </c>
       <c r="N5">
-        <v>345.0298758</v>
+        <v>343.6648344</v>
       </c>
       <c r="O5">
-        <v>86.25746894999999</v>
+        <v>85.91620859999999</v>
       </c>
       <c r="P5">
-        <v>258.77240685</v>
+        <v>257.7486258</v>
       </c>
       <c r="Q5">
-        <v>270.77240685</v>
+        <v>269.7486258</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1016581345688018</v>
+        <v>0.1020978239152187</v>
       </c>
       <c r="T5">
-        <v>0.8641075767637914</v>
+        <v>0.8709094311148918</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>85.25382453601773</v>
+        <v>63.9403684020133</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09952291095860995</v>
+        <v>0.09930568138548214</v>
       </c>
       <c r="C6">
-        <v>2461.801513242074</v>
+        <v>2444.384432182465</v>
       </c>
       <c r="D6">
-        <v>2394.353513242074</v>
+        <v>2404.074432182465</v>
       </c>
       <c r="E6">
-        <v>-1629.048</v>
+        <v>-1601.91</v>
       </c>
       <c r="F6">
-        <v>108.552</v>
+        <v>135.69</v>
       </c>
       <c r="G6">
         <v>176</v>
@@ -1779,28 +1779,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M6">
-        <v>5.4601656</v>
+        <v>6.825207000000001</v>
       </c>
       <c r="N6">
-        <v>343.6648344</v>
+        <v>342.299793</v>
       </c>
       <c r="O6">
-        <v>85.91620859999999</v>
+        <v>85.57494824999999</v>
       </c>
       <c r="P6">
-        <v>257.7486258</v>
+        <v>256.72484475</v>
       </c>
       <c r="Q6">
-        <v>269.7486258</v>
+        <v>268.72484475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1020978239152187</v>
+        <v>0.1025467698794549</v>
       </c>
       <c r="T6">
-        <v>0.8709094311148918</v>
+        <v>0.8778544823996995</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.9403684020133</v>
+        <v>51.15229472161063</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09930568138548214</v>
+        <v>0.09908845181235433</v>
       </c>
       <c r="C7">
-        <v>2444.384432182465</v>
+        <v>2427.046605482853</v>
       </c>
       <c r="D7">
-        <v>2404.074432182465</v>
+        <v>2413.874605482853</v>
       </c>
       <c r="E7">
-        <v>-1601.91</v>
+        <v>-1574.772</v>
       </c>
       <c r="F7">
-        <v>135.69</v>
+        <v>162.828</v>
       </c>
       <c r="G7">
         <v>176</v>
@@ -1861,28 +1861,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M7">
-        <v>6.825207000000001</v>
+        <v>8.190248400000002</v>
       </c>
       <c r="N7">
-        <v>342.299793</v>
+        <v>340.9347515999999</v>
       </c>
       <c r="O7">
-        <v>85.57494824999999</v>
+        <v>85.23368789999998</v>
       </c>
       <c r="P7">
-        <v>256.72484475</v>
+        <v>255.7010636999999</v>
       </c>
       <c r="Q7">
-        <v>268.72484475</v>
+        <v>267.7010637</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1025467698794549</v>
+        <v>0.1030052678854833</v>
       </c>
       <c r="T7">
-        <v>0.8778544823996995</v>
+        <v>0.8849473007331202</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.15229472161063</v>
+        <v>42.62691226800885</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09908845181235433</v>
+        <v>0.09887122223922652</v>
       </c>
       <c r="C8">
-        <v>2427.046605482853</v>
+        <v>2409.789006348118</v>
       </c>
       <c r="D8">
-        <v>2413.874605482853</v>
+        <v>2423.755006348118</v>
       </c>
       <c r="E8">
-        <v>-1574.772</v>
+        <v>-1547.634</v>
       </c>
       <c r="F8">
-        <v>162.828</v>
+        <v>189.966</v>
       </c>
       <c r="G8">
         <v>176</v>
@@ -1943,28 +1943,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M8">
-        <v>8.1902484</v>
+        <v>9.555289799999999</v>
       </c>
       <c r="N8">
-        <v>340.9347516</v>
+        <v>339.5697101999999</v>
       </c>
       <c r="O8">
-        <v>85.23368789999999</v>
+        <v>84.89242754999998</v>
       </c>
       <c r="P8">
-        <v>255.7010637</v>
+        <v>254.6772826499999</v>
       </c>
       <c r="Q8">
-        <v>267.7010637</v>
+        <v>266.6772826499999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1030052678854833</v>
+        <v>0.1034736260636844</v>
       </c>
       <c r="T8">
-        <v>0.8849473007331202</v>
+        <v>0.8921926527941413</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.62691226800887</v>
+        <v>36.53735337257903</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09887122223922651</v>
+        <v>0.09865399266609873</v>
       </c>
       <c r="C9">
-        <v>2409.789006348119</v>
+        <v>2392.612623982599</v>
       </c>
       <c r="D9">
-        <v>2423.755006348119</v>
+        <v>2433.716623982599</v>
       </c>
       <c r="E9">
-        <v>-1547.634</v>
+        <v>-1520.496</v>
       </c>
       <c r="F9">
-        <v>189.966</v>
+        <v>217.104</v>
       </c>
       <c r="G9">
         <v>176</v>
@@ -2025,28 +2025,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M9">
-        <v>9.555289800000001</v>
+        <v>10.9203312</v>
       </c>
       <c r="N9">
-        <v>339.5697101999999</v>
+        <v>338.2046687999999</v>
       </c>
       <c r="O9">
-        <v>84.89242754999998</v>
+        <v>84.55116719999998</v>
       </c>
       <c r="P9">
-        <v>254.6772826499999</v>
+        <v>253.6535015999999</v>
       </c>
       <c r="Q9">
-        <v>266.6772826499999</v>
+        <v>265.6535015999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1034736260636844</v>
+        <v>0.1039521659414117</v>
       </c>
       <c r="T9">
-        <v>0.8921926527941413</v>
+        <v>0.899595512508663</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.53735337257902</v>
+        <v>31.97018420100665</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09865399266609873</v>
+        <v>0.09843676309297093</v>
       </c>
       <c r="C10">
-        <v>2392.612623982599</v>
+        <v>2375.518463920248</v>
       </c>
       <c r="D10">
-        <v>2433.716623982599</v>
+        <v>2443.760463920249</v>
       </c>
       <c r="E10">
-        <v>-1520.496</v>
+        <v>-1493.358</v>
       </c>
       <c r="F10">
-        <v>217.104</v>
+        <v>244.242</v>
       </c>
       <c r="G10">
         <v>176</v>
@@ -2107,28 +2107,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M10">
-        <v>10.9203312</v>
+        <v>12.2853726</v>
       </c>
       <c r="N10">
-        <v>338.2046687999999</v>
+        <v>336.8396273999999</v>
       </c>
       <c r="O10">
-        <v>84.55116719999998</v>
+        <v>84.20990684999998</v>
       </c>
       <c r="P10">
-        <v>253.6535015999999</v>
+        <v>252.6297205499999</v>
       </c>
       <c r="Q10">
-        <v>265.6535015999999</v>
+        <v>264.6297205499999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1039521659414117</v>
+        <v>0.1044412231790889</v>
       </c>
       <c r="T10">
-        <v>0.899595512508663</v>
+        <v>0.9071610724366904</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.97018420100665</v>
+        <v>28.4179415120059</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09843676309297093</v>
+        <v>0.09821953351984312</v>
       </c>
       <c r="C11">
-        <v>2375.518463920248</v>
+        <v>2358.507548362979</v>
       </c>
       <c r="D11">
-        <v>2443.760463920249</v>
+        <v>2453.887548362979</v>
       </c>
       <c r="E11">
-        <v>-1493.358</v>
+        <v>-1466.22</v>
       </c>
       <c r="F11">
-        <v>244.242</v>
+        <v>271.38</v>
       </c>
       <c r="G11">
         <v>176</v>
@@ -2189,28 +2189,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M11">
-        <v>12.2853726</v>
+        <v>13.650414</v>
       </c>
       <c r="N11">
-        <v>336.8396273999999</v>
+        <v>335.4745859999999</v>
       </c>
       <c r="O11">
-        <v>84.20990684999998</v>
+        <v>83.86864649999998</v>
       </c>
       <c r="P11">
-        <v>252.6297205499999</v>
+        <v>251.6059394999999</v>
       </c>
       <c r="Q11">
-        <v>264.6297205499999</v>
+        <v>263.6059395</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1044412231790889</v>
+        <v>0.1049411483553813</v>
       </c>
       <c r="T11">
-        <v>0.9071610724366904</v>
+        <v>0.9148947559186742</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.4179415120059</v>
+        <v>25.57614736080532</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09821953351984312</v>
+        <v>0.09800230394671533</v>
       </c>
       <c r="C12">
-        <v>2358.507548362979</v>
+        <v>2341.580916527469</v>
       </c>
       <c r="D12">
-        <v>2453.887548362979</v>
+        <v>2464.098916527469</v>
       </c>
       <c r="E12">
-        <v>-1466.22</v>
+        <v>-1439.082</v>
       </c>
       <c r="F12">
-        <v>271.3800000000001</v>
+        <v>298.518</v>
       </c>
       <c r="G12">
         <v>176</v>
@@ -2271,28 +2271,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M12">
-        <v>13.650414</v>
+        <v>15.0154554</v>
       </c>
       <c r="N12">
-        <v>335.4745859999999</v>
+        <v>334.1095445999999</v>
       </c>
       <c r="O12">
-        <v>83.86864649999998</v>
+        <v>83.52738614999998</v>
       </c>
       <c r="P12">
-        <v>251.6059394999999</v>
+        <v>250.58215845</v>
       </c>
       <c r="Q12">
-        <v>263.6059395</v>
+        <v>262.58215845</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1049411483553813</v>
+        <v>0.1054523078052981</v>
       </c>
       <c r="T12">
-        <v>0.9148947559186742</v>
+        <v>0.9228022300407026</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.57614736080531</v>
+        <v>23.25104305527756</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09800230394671533</v>
+        <v>0.09778507437358752</v>
       </c>
       <c r="C13">
-        <v>2341.580916527469</v>
+        <v>2324.73962500066</v>
       </c>
       <c r="D13">
-        <v>2464.098916527469</v>
+        <v>2474.395625000659</v>
       </c>
       <c r="E13">
-        <v>-1439.082</v>
+        <v>-1411.944</v>
       </c>
       <c r="F13">
-        <v>298.518</v>
+        <v>325.656</v>
       </c>
       <c r="G13">
         <v>176</v>
@@ -2353,28 +2353,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M13">
-        <v>15.0154554</v>
+        <v>16.3804968</v>
       </c>
       <c r="N13">
-        <v>334.1095445999999</v>
+        <v>332.7445031999999</v>
       </c>
       <c r="O13">
-        <v>83.52738614999998</v>
+        <v>83.18612579999999</v>
       </c>
       <c r="P13">
-        <v>250.58215845</v>
+        <v>249.5583774</v>
       </c>
       <c r="Q13">
-        <v>262.58215845</v>
+        <v>261.5583773999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1054523078052981</v>
+        <v>0.1059750845154404</v>
       </c>
       <c r="T13">
-        <v>0.9228022300407026</v>
+        <v>0.930889419483686</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.25104305527756</v>
+        <v>21.31345613400443</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09778507437358752</v>
+        <v>0.09756784480045971</v>
       </c>
       <c r="C14">
-        <v>2324.73962500066</v>
+        <v>2307.984748104201</v>
       </c>
       <c r="D14">
-        <v>2474.395625000659</v>
+        <v>2484.778748104201</v>
       </c>
       <c r="E14">
-        <v>-1411.944</v>
+        <v>-1384.806</v>
       </c>
       <c r="F14">
-        <v>325.656</v>
+        <v>352.794</v>
       </c>
       <c r="G14">
         <v>176</v>
@@ -2435,28 +2435,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M14">
-        <v>16.3804968</v>
+        <v>17.7455382</v>
       </c>
       <c r="N14">
-        <v>332.7445031999999</v>
+        <v>331.3794617999999</v>
       </c>
       <c r="O14">
-        <v>83.18612579999999</v>
+        <v>82.84486544999999</v>
       </c>
       <c r="P14">
-        <v>249.5583774</v>
+        <v>248.53459635</v>
       </c>
       <c r="Q14">
-        <v>261.5583773999999</v>
+        <v>260.53459635</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1059750845154404</v>
+        <v>0.1065098790809882</v>
       </c>
       <c r="T14">
-        <v>0.930889419483686</v>
+        <v>0.9391625213276575</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.31345613400443</v>
+        <v>19.67395950831178</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09756784480045971</v>
+        <v>0.09735061522733189</v>
       </c>
       <c r="C15">
-        <v>2307.984748104201</v>
+        <v>2291.317378268117</v>
       </c>
       <c r="D15">
-        <v>2484.778748104201</v>
+        <v>2495.249378268118</v>
       </c>
       <c r="E15">
-        <v>-1384.806</v>
+        <v>-1357.668</v>
       </c>
       <c r="F15">
-        <v>352.794</v>
+        <v>379.9320000000001</v>
       </c>
       <c r="G15">
         <v>176</v>
@@ -2517,28 +2517,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M15">
-        <v>17.7455382</v>
+        <v>19.1105796</v>
       </c>
       <c r="N15">
-        <v>331.3794617999999</v>
+        <v>330.0144203999999</v>
       </c>
       <c r="O15">
-        <v>82.84486544999999</v>
+        <v>82.50360509999999</v>
       </c>
       <c r="P15">
-        <v>248.53459635</v>
+        <v>247.5108153</v>
       </c>
       <c r="Q15">
-        <v>260.53459635</v>
+        <v>259.5108153</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1065098790809882</v>
+        <v>0.1070571107294557</v>
       </c>
       <c r="T15">
-        <v>0.9391625213276575</v>
+        <v>0.9476280208889308</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.67395950831178</v>
+        <v>18.26867668628951</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09735061522733189</v>
+        <v>0.09713338565420411</v>
       </c>
       <c r="C16">
-        <v>2291.317378268117</v>
+        <v>2274.738626413951</v>
       </c>
       <c r="D16">
-        <v>2495.249378268118</v>
+        <v>2505.808626413952</v>
       </c>
       <c r="E16">
-        <v>-1357.668</v>
+        <v>-1330.53</v>
       </c>
       <c r="F16">
-        <v>379.9320000000001</v>
+        <v>407.0700000000001</v>
       </c>
       <c r="G16">
         <v>176</v>
@@ -2599,28 +2599,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M16">
-        <v>19.1105796</v>
+        <v>20.475621</v>
       </c>
       <c r="N16">
-        <v>330.0144203999999</v>
+        <v>328.649379</v>
       </c>
       <c r="O16">
-        <v>82.50360509999999</v>
+        <v>82.16234474999999</v>
       </c>
       <c r="P16">
-        <v>247.5108153</v>
+        <v>246.48703425</v>
       </c>
       <c r="Q16">
-        <v>259.5108153</v>
+        <v>258.48703425</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1070571107294557</v>
+        <v>0.1076172184167107</v>
       </c>
       <c r="T16">
-        <v>0.9476280208889308</v>
+        <v>0.9562927086751752</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.26867668628951</v>
+        <v>17.05076490720354</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09713338565420411</v>
+        <v>0.0969161560810763</v>
       </c>
       <c r="C17">
-        <v>2274.738626413951</v>
+        <v>2258.249622347693</v>
       </c>
       <c r="D17">
-        <v>2505.808626413952</v>
+        <v>2516.457622347693</v>
       </c>
       <c r="E17">
-        <v>-1330.53</v>
+        <v>-1303.392</v>
       </c>
       <c r="F17">
-        <v>407.07</v>
+        <v>434.208</v>
       </c>
       <c r="G17">
         <v>176</v>
@@ -2681,28 +2681,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M17">
-        <v>20.475621</v>
+        <v>21.8406624</v>
       </c>
       <c r="N17">
-        <v>328.649379</v>
+        <v>327.2843376</v>
       </c>
       <c r="O17">
-        <v>82.16234474999999</v>
+        <v>81.82108439999999</v>
       </c>
       <c r="P17">
-        <v>246.48703425</v>
+        <v>245.4632532</v>
       </c>
       <c r="Q17">
-        <v>258.48703425</v>
+        <v>257.4632531999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1076172184167107</v>
+        <v>0.1081906620012813</v>
       </c>
       <c r="T17">
-        <v>0.9562927086751752</v>
+        <v>0.9651636985515684</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.05076490720354</v>
+        <v>15.98509210050332</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0969161560810763</v>
+        <v>0.09669892650794849</v>
       </c>
       <c r="C18">
-        <v>2258.249622347693</v>
+        <v>2241.85151516275</v>
       </c>
       <c r="D18">
-        <v>2516.457622347693</v>
+        <v>2527.19751516275</v>
       </c>
       <c r="E18">
-        <v>-1303.392</v>
+        <v>-1276.254</v>
       </c>
       <c r="F18">
-        <v>434.208</v>
+        <v>461.3460000000001</v>
       </c>
       <c r="G18">
         <v>176</v>
@@ -2763,28 +2763,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M18">
-        <v>21.8406624</v>
+        <v>23.2057038</v>
       </c>
       <c r="N18">
-        <v>327.2843376</v>
+        <v>325.9192962</v>
       </c>
       <c r="O18">
-        <v>81.82108439999999</v>
+        <v>81.47982404999999</v>
       </c>
       <c r="P18">
-        <v>245.4632532</v>
+        <v>244.43947215</v>
       </c>
       <c r="Q18">
-        <v>257.4632531999999</v>
+        <v>256.43947215</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1081906620012813</v>
+        <v>0.1087779235035524</v>
       </c>
       <c r="T18">
-        <v>0.9651636985515684</v>
+        <v>0.9742484472201638</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.98509210050332</v>
+        <v>15.0447925651796</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09669892650794849</v>
+        <v>0.09648169693482071</v>
       </c>
       <c r="C19">
-        <v>2241.85151516275</v>
+        <v>2225.545473653296</v>
       </c>
       <c r="D19">
-        <v>2527.19751516275</v>
+        <v>2538.029473653296</v>
       </c>
       <c r="E19">
-        <v>-1276.254</v>
+        <v>-1249.116</v>
       </c>
       <c r="F19">
-        <v>461.3460000000001</v>
+        <v>488.4840000000001</v>
       </c>
       <c r="G19">
         <v>176</v>
@@ -2845,28 +2845,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M19">
-        <v>23.2057038</v>
+        <v>24.5707452</v>
       </c>
       <c r="N19">
-        <v>325.9192962</v>
+        <v>324.5542548</v>
       </c>
       <c r="O19">
-        <v>81.47982404999999</v>
+        <v>81.13856369999999</v>
       </c>
       <c r="P19">
-        <v>244.43947215</v>
+        <v>243.4156911</v>
       </c>
       <c r="Q19">
-        <v>256.43947215</v>
+        <v>255.4156911</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1087779235035524</v>
+        <v>0.1093795084570984</v>
       </c>
       <c r="T19">
-        <v>0.9742484472201638</v>
+        <v>0.9835547751245785</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.0447925651796</v>
+        <v>14.20897075600295</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09648169693482073</v>
+        <v>0.09626446736169292</v>
       </c>
       <c r="C20">
-        <v>2225.545473653295</v>
+        <v>2209.332686738294</v>
       </c>
       <c r="D20">
-        <v>2538.029473653295</v>
+        <v>2548.954686738294</v>
       </c>
       <c r="E20">
-        <v>-1249.116</v>
+        <v>-1221.978</v>
       </c>
       <c r="F20">
-        <v>488.484</v>
+        <v>515.6220000000001</v>
       </c>
       <c r="G20">
         <v>176</v>
@@ -2927,28 +2927,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M20">
-        <v>24.5707452</v>
+        <v>25.9357866</v>
       </c>
       <c r="N20">
-        <v>324.5542548</v>
+        <v>323.1892133999999</v>
       </c>
       <c r="O20">
-        <v>81.13856369999999</v>
+        <v>80.79730334999998</v>
       </c>
       <c r="P20">
-        <v>243.4156911</v>
+        <v>242.3919100499999</v>
       </c>
       <c r="Q20">
-        <v>255.4156911</v>
+        <v>254.3919100499999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1093795084570984</v>
+        <v>0.1099959473601147</v>
       </c>
       <c r="T20">
-        <v>0.9835547751245785</v>
+        <v>0.9930908889031763</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.20897075600295</v>
+        <v>13.46113018989753</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09626446736169292</v>
+        <v>0.0962722377885651</v>
       </c>
       <c r="C21">
-        <v>2209.332686738294</v>
+        <v>2181.80226375763</v>
       </c>
       <c r="D21">
-        <v>2548.954686738294</v>
+        <v>2548.56226375763</v>
       </c>
       <c r="E21">
-        <v>-1221.978</v>
+        <v>-1194.84</v>
       </c>
       <c r="F21">
-        <v>515.6220000000001</v>
+        <v>542.7600000000001</v>
       </c>
       <c r="G21">
         <v>176</v>
@@ -3009,45 +3009,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M21">
-        <v>25.9357866</v>
+        <v>28.114968</v>
       </c>
       <c r="N21">
-        <v>323.1892133999999</v>
+        <v>321.0100319999999</v>
       </c>
       <c r="O21">
-        <v>80.79730334999998</v>
+        <v>80.25250799999998</v>
       </c>
       <c r="P21">
-        <v>242.3919100499999</v>
+        <v>240.7575239999999</v>
       </c>
       <c r="Q21">
-        <v>254.3919100499999</v>
+        <v>252.7575239999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1099959473601147</v>
+        <v>0.1106277972357064</v>
       </c>
       <c r="T21">
-        <v>0.9930908889031763</v>
+        <v>1.002865405526239</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.46113018989753</v>
+        <v>12.41776266649138</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0962722377885651</v>
+        <v>0.09606625821543728</v>
       </c>
       <c r="C22">
-        <v>2181.80226375763</v>
+        <v>2165.107686160956</v>
       </c>
       <c r="D22">
-        <v>2548.56226375763</v>
+        <v>2559.005686160956</v>
       </c>
       <c r="E22">
-        <v>-1194.84</v>
+        <v>-1167.702</v>
       </c>
       <c r="F22">
-        <v>542.7600000000001</v>
+        <v>569.8980000000001</v>
       </c>
       <c r="G22">
         <v>176</v>
@@ -3091,28 +3091,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M22">
-        <v>28.114968</v>
+        <v>29.5207164</v>
       </c>
       <c r="N22">
-        <v>321.0100319999999</v>
+        <v>319.6042835999999</v>
       </c>
       <c r="O22">
-        <v>80.25250799999998</v>
+        <v>79.90107089999998</v>
       </c>
       <c r="P22">
-        <v>240.7575239999999</v>
+        <v>239.7032126999999</v>
       </c>
       <c r="Q22">
-        <v>252.7575239999999</v>
+        <v>251.7032126999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1106277972357064</v>
+        <v>0.1112756433106801</v>
       </c>
       <c r="T22">
-        <v>1.002865405526239</v>
+        <v>1.012887378266341</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.41776266649138</v>
+        <v>11.8264406347537</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09606625821543728</v>
+        <v>0.09586027864230948</v>
       </c>
       <c r="C23">
-        <v>2165.107686160956</v>
+        <v>2148.499050222896</v>
       </c>
       <c r="D23">
-        <v>2559.005686160956</v>
+        <v>2569.535050222896</v>
       </c>
       <c r="E23">
-        <v>-1167.702</v>
+        <v>-1140.564</v>
       </c>
       <c r="F23">
-        <v>569.898</v>
+        <v>597.0360000000001</v>
       </c>
       <c r="G23">
         <v>176</v>
@@ -3173,28 +3173,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M23">
-        <v>29.5207164</v>
+        <v>30.9264648</v>
       </c>
       <c r="N23">
-        <v>319.6042835999999</v>
+        <v>318.1985351999999</v>
       </c>
       <c r="O23">
-        <v>79.90107089999998</v>
+        <v>79.54963379999998</v>
       </c>
       <c r="P23">
-        <v>239.7032126999999</v>
+        <v>238.6489013999999</v>
       </c>
       <c r="Q23">
-        <v>251.7032126999999</v>
+        <v>250.6489013999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1112756433106801</v>
+        <v>0.1119401008234737</v>
       </c>
       <c r="T23">
-        <v>1.012887378266341</v>
+        <v>1.023166324666446</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.8264406347537</v>
+        <v>11.2888751513558</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09586027864230948</v>
+        <v>0.09565429906918169</v>
       </c>
       <c r="C24">
-        <v>2148.499050222896</v>
+        <v>2131.977421181143</v>
       </c>
       <c r="D24">
-        <v>2569.535050222896</v>
+        <v>2580.151421181143</v>
       </c>
       <c r="E24">
-        <v>-1140.564</v>
+        <v>-1113.426</v>
       </c>
       <c r="F24">
-        <v>597.0360000000001</v>
+        <v>624.1740000000001</v>
       </c>
       <c r="G24">
         <v>176</v>
@@ -3255,28 +3255,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M24">
-        <v>30.9264648</v>
+        <v>32.33221320000001</v>
       </c>
       <c r="N24">
-        <v>318.1985351999999</v>
+        <v>316.7927867999999</v>
       </c>
       <c r="O24">
-        <v>79.54963379999998</v>
+        <v>79.19819669999998</v>
       </c>
       <c r="P24">
-        <v>238.6489013999999</v>
+        <v>237.5945900999999</v>
       </c>
       <c r="Q24">
-        <v>250.6489013999999</v>
+        <v>249.5945900999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1119401008234737</v>
+        <v>0.1126218169729632</v>
       </c>
       <c r="T24">
-        <v>1.023166324666446</v>
+        <v>1.033712256687333</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.2888751513558</v>
+        <v>10.7980544926012</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09565429906918169</v>
+        <v>0.0954483194960539</v>
       </c>
       <c r="C25">
-        <v>2131.977421181143</v>
+        <v>2115.543881951103</v>
       </c>
       <c r="D25">
-        <v>2580.151421181143</v>
+        <v>2590.855881951103</v>
       </c>
       <c r="E25">
-        <v>-1113.426</v>
+        <v>-1086.288</v>
       </c>
       <c r="F25">
-        <v>624.1740000000001</v>
+        <v>651.3120000000001</v>
       </c>
       <c r="G25">
         <v>176</v>
@@ -3337,28 +3337,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M25">
-        <v>32.33221320000001</v>
+        <v>33.73796160000001</v>
       </c>
       <c r="N25">
-        <v>316.7927867999999</v>
+        <v>315.3870383999999</v>
       </c>
       <c r="O25">
-        <v>79.19819669999998</v>
+        <v>78.84675959999998</v>
       </c>
       <c r="P25">
-        <v>237.5945900999999</v>
+        <v>236.5402788</v>
       </c>
       <c r="Q25">
-        <v>249.5945900999999</v>
+        <v>248.5402788</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1126218169729632</v>
+        <v>0.1133214730211236</v>
       </c>
       <c r="T25">
-        <v>1.033712256687333</v>
+        <v>1.044535713235086</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.7980544926012</v>
+        <v>10.34813555540948</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0954483194960539</v>
+        <v>0.09524233992292606</v>
       </c>
       <c r="C26">
-        <v>2115.543881951103</v>
+        <v>2099.199533494131</v>
       </c>
       <c r="D26">
-        <v>2590.855881951103</v>
+        <v>2601.649533494131</v>
       </c>
       <c r="E26">
-        <v>-1086.288</v>
+        <v>-1059.15</v>
       </c>
       <c r="F26">
-        <v>651.312</v>
+        <v>678.45</v>
       </c>
       <c r="G26">
         <v>176</v>
@@ -3419,28 +3419,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M26">
-        <v>33.7379616</v>
+        <v>35.14371</v>
       </c>
       <c r="N26">
-        <v>315.3870383999999</v>
+        <v>313.9812899999999</v>
       </c>
       <c r="O26">
-        <v>78.84675959999998</v>
+        <v>78.49532249999999</v>
       </c>
       <c r="P26">
-        <v>236.5402788</v>
+        <v>235.4859675</v>
       </c>
       <c r="Q26">
-        <v>248.5402788</v>
+        <v>247.4859675</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1133214730211236</v>
+        <v>0.1140397865639014</v>
       </c>
       <c r="T26">
-        <v>1.044535713235086</v>
+        <v>1.055647795290778</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.34813555540949</v>
+        <v>9.934210133193108</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09524233992292606</v>
+        <v>0.09536786034979827</v>
       </c>
       <c r="C27">
-        <v>2099.199533494131</v>
+        <v>2065.473390336215</v>
       </c>
       <c r="D27">
-        <v>2601.649533494131</v>
+        <v>2595.061390336215</v>
       </c>
       <c r="E27">
-        <v>-1059.15</v>
+        <v>-1032.012</v>
       </c>
       <c r="F27">
-        <v>678.45</v>
+        <v>705.5880000000001</v>
       </c>
       <c r="G27">
         <v>176</v>
@@ -3501,45 +3501,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M27">
-        <v>35.14371</v>
+        <v>37.748958</v>
       </c>
       <c r="N27">
-        <v>313.9812899999999</v>
+        <v>311.3760419999999</v>
       </c>
       <c r="O27">
-        <v>78.49532249999999</v>
+        <v>77.84401049999998</v>
       </c>
       <c r="P27">
-        <v>235.4859675</v>
+        <v>233.5320315</v>
       </c>
       <c r="Q27">
-        <v>247.4859675</v>
+        <v>245.5320315</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1140397865639014</v>
+        <v>0.1147775139862139</v>
       </c>
       <c r="T27">
-        <v>1.055647795290778</v>
+        <v>1.067060203888516</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.934210133193108</v>
+        <v>9.248599656711052</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09536786034979827</v>
+        <v>0.09517463077667047</v>
       </c>
       <c r="C28">
-        <v>2065.473390336215</v>
+        <v>2048.491265870013</v>
       </c>
       <c r="D28">
-        <v>2595.061390336215</v>
+        <v>2605.217265870013</v>
       </c>
       <c r="E28">
-        <v>-1032.012</v>
+        <v>-1004.874</v>
       </c>
       <c r="F28">
-        <v>705.5880000000001</v>
+        <v>732.7260000000001</v>
       </c>
       <c r="G28">
         <v>176</v>
@@ -3583,28 +3583,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M28">
-        <v>37.748958</v>
+        <v>39.200841</v>
       </c>
       <c r="N28">
-        <v>311.3760419999999</v>
+        <v>309.9241589999999</v>
       </c>
       <c r="O28">
-        <v>77.84401049999998</v>
+        <v>77.48103974999998</v>
       </c>
       <c r="P28">
-        <v>233.5320315</v>
+        <v>232.4431192499999</v>
       </c>
       <c r="Q28">
-        <v>245.5320315</v>
+        <v>244.4431192499999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1147775139862139</v>
+        <v>0.1155354531187267</v>
       </c>
       <c r="T28">
-        <v>1.067060203888516</v>
+        <v>1.078785281214959</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.248599656711052</v>
+        <v>8.906058928684715</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09517463077667047</v>
+        <v>0.09498140120354268</v>
       </c>
       <c r="C29">
-        <v>2048.491265870013</v>
+        <v>2031.588944558911</v>
       </c>
       <c r="D29">
-        <v>2605.217265870013</v>
+        <v>2615.452944558911</v>
       </c>
       <c r="E29">
-        <v>-1004.874</v>
+        <v>-977.7359999999998</v>
       </c>
       <c r="F29">
-        <v>732.7260000000001</v>
+        <v>759.8640000000001</v>
       </c>
       <c r="G29">
         <v>176</v>
@@ -3665,28 +3665,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M29">
-        <v>39.200841</v>
+        <v>40.65272400000001</v>
       </c>
       <c r="N29">
-        <v>309.9241589999999</v>
+        <v>308.472276</v>
       </c>
       <c r="O29">
-        <v>77.48103974999998</v>
+        <v>77.11806899999999</v>
       </c>
       <c r="P29">
-        <v>232.4431192499999</v>
+        <v>231.354207</v>
       </c>
       <c r="Q29">
-        <v>244.4431192499999</v>
+        <v>243.354207</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1155354531187267</v>
+        <v>0.1163144461160315</v>
       </c>
       <c r="T29">
-        <v>1.078785281214959</v>
+        <v>1.090836055133804</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.906058928684715</v>
+        <v>8.587985395517405</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09498140120354268</v>
+        <v>0.09478817163041488</v>
       </c>
       <c r="C30">
-        <v>2031.588944558911</v>
+        <v>2014.767370732677</v>
       </c>
       <c r="D30">
-        <v>2615.452944558911</v>
+        <v>2625.769370732677</v>
       </c>
       <c r="E30">
-        <v>-977.7359999999998</v>
+        <v>-950.5979999999997</v>
       </c>
       <c r="F30">
-        <v>759.8640000000001</v>
+        <v>787.0020000000002</v>
       </c>
       <c r="G30">
         <v>176</v>
@@ -3747,28 +3747,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M30">
-        <v>40.65272400000001</v>
+        <v>42.10460700000001</v>
       </c>
       <c r="N30">
-        <v>308.472276</v>
+        <v>307.020393</v>
       </c>
       <c r="O30">
-        <v>77.11806899999999</v>
+        <v>76.75509824999999</v>
       </c>
       <c r="P30">
-        <v>231.354207</v>
+        <v>230.26529475</v>
       </c>
       <c r="Q30">
-        <v>243.354207</v>
+        <v>242.26529475</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1163144461160315</v>
+        <v>0.1171153825780491</v>
       </c>
       <c r="T30">
-        <v>1.090836055133804</v>
+        <v>1.103226287472898</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.587985395517405</v>
+        <v>8.29184796808577</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09478817163041488</v>
+        <v>0.09459494205728705</v>
       </c>
       <c r="C31">
-        <v>2014.767370732677</v>
+        <v>1998.027503679389</v>
       </c>
       <c r="D31">
-        <v>2625.769370732677</v>
+        <v>2636.167503679389</v>
       </c>
       <c r="E31">
-        <v>-950.598</v>
+        <v>-923.4599999999999</v>
       </c>
       <c r="F31">
-        <v>787.002</v>
+        <v>814.14</v>
       </c>
       <c r="G31">
         <v>176</v>
@@ -3829,28 +3829,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M31">
-        <v>42.10460699999999</v>
+        <v>43.55649</v>
       </c>
       <c r="N31">
-        <v>307.020393</v>
+        <v>305.5685099999999</v>
       </c>
       <c r="O31">
-        <v>76.75509824999999</v>
+        <v>76.39212749999999</v>
       </c>
       <c r="P31">
-        <v>230.26529475</v>
+        <v>229.1763825</v>
       </c>
       <c r="Q31">
-        <v>242.26529475</v>
+        <v>241.1763825</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1171153825780491</v>
+        <v>0.1179392029389815</v>
       </c>
       <c r="T31">
-        <v>1.103226287472898</v>
+        <v>1.115970526450251</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.291847968085772</v>
+        <v>8.015453035816247</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09459494205728705</v>
+        <v>0.09440171248415925</v>
       </c>
       <c r="C32">
-        <v>1998.027503679389</v>
+        <v>1981.370317942783</v>
       </c>
       <c r="D32">
-        <v>2636.167503679389</v>
+        <v>2646.648317942783</v>
       </c>
       <c r="E32">
-        <v>-923.4599999999999</v>
+        <v>-896.3219999999999</v>
       </c>
       <c r="F32">
-        <v>814.14</v>
+        <v>841.278</v>
       </c>
       <c r="G32">
         <v>176</v>
@@ -3911,28 +3911,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M32">
-        <v>43.55649</v>
+        <v>45.008373</v>
       </c>
       <c r="N32">
-        <v>305.5685099999999</v>
+        <v>304.1166269999999</v>
       </c>
       <c r="O32">
-        <v>76.39212749999999</v>
+        <v>76.02915674999998</v>
       </c>
       <c r="P32">
-        <v>229.1763825</v>
+        <v>228.08747025</v>
       </c>
       <c r="Q32">
-        <v>241.1763825</v>
+        <v>240.08747025</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1179392029389815</v>
+        <v>0.1187869021509554</v>
       </c>
       <c r="T32">
-        <v>1.115970526450251</v>
+        <v>1.129084163658832</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.015453035816247</v>
+        <v>7.756890034660882</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09440171248415925</v>
+        <v>0.09440048291103147</v>
       </c>
       <c r="C33">
-        <v>1981.370317942783</v>
+        <v>1954.299277105646</v>
       </c>
       <c r="D33">
-        <v>2646.648317942783</v>
+        <v>2646.715277105646</v>
       </c>
       <c r="E33">
-        <v>-896.3219999999999</v>
+        <v>-869.1839999999999</v>
       </c>
       <c r="F33">
-        <v>841.278</v>
+        <v>868.4160000000001</v>
       </c>
       <c r="G33">
         <v>176</v>
@@ -3993,45 +3993,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M33">
-        <v>45.008373</v>
+        <v>47.15498880000001</v>
       </c>
       <c r="N33">
-        <v>304.1166269999999</v>
+        <v>301.9700111999999</v>
       </c>
       <c r="O33">
-        <v>76.02915674999998</v>
+        <v>75.49250279999998</v>
       </c>
       <c r="P33">
-        <v>228.08747025</v>
+        <v>226.4775083999999</v>
       </c>
       <c r="Q33">
-        <v>240.08747025</v>
+        <v>238.4775083999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1187869021509554</v>
+        <v>0.1196595336926933</v>
       </c>
       <c r="T33">
-        <v>1.129084163658832</v>
+        <v>1.14258349607943</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.756890034660882</v>
+        <v>7.403776543787449</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09440048291103147</v>
+        <v>0.09421325333790366</v>
       </c>
       <c r="C34">
-        <v>1954.299277105646</v>
+        <v>1937.396973683702</v>
       </c>
       <c r="D34">
-        <v>2646.715277105646</v>
+        <v>2656.950973683702</v>
       </c>
       <c r="E34">
-        <v>-869.1839999999999</v>
+        <v>-842.0459999999998</v>
       </c>
       <c r="F34">
-        <v>868.4160000000001</v>
+        <v>895.5540000000001</v>
       </c>
       <c r="G34">
         <v>176</v>
@@ -4075,28 +4075,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M34">
-        <v>47.15498880000001</v>
+        <v>48.6285822</v>
       </c>
       <c r="N34">
-        <v>301.9700111999999</v>
+        <v>300.4964178</v>
       </c>
       <c r="O34">
-        <v>75.49250279999998</v>
+        <v>75.12410444999999</v>
       </c>
       <c r="P34">
-        <v>226.4775083999999</v>
+        <v>225.37231335</v>
       </c>
       <c r="Q34">
-        <v>238.4775083999999</v>
+        <v>237.37231335</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1196595336926933</v>
+        <v>0.1205582139371696</v>
       </c>
       <c r="T34">
-        <v>1.14258349607943</v>
+        <v>1.156485793646912</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.403776543787449</v>
+        <v>7.179419678824194</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09421325333790366</v>
+        <v>0.09402602376477585</v>
       </c>
       <c r="C35">
-        <v>1937.396973683702</v>
+        <v>1920.574147065</v>
       </c>
       <c r="D35">
-        <v>2656.950973683702</v>
+        <v>2667.266147065</v>
       </c>
       <c r="E35">
-        <v>-842.0459999999998</v>
+        <v>-814.9079999999998</v>
       </c>
       <c r="F35">
-        <v>895.5540000000001</v>
+        <v>922.6920000000001</v>
       </c>
       <c r="G35">
         <v>176</v>
@@ -4157,28 +4157,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M35">
-        <v>48.6285822</v>
+        <v>50.10217560000001</v>
       </c>
       <c r="N35">
-        <v>300.4964178</v>
+        <v>299.0228243999999</v>
       </c>
       <c r="O35">
-        <v>75.12410444999999</v>
+        <v>74.75570609999998</v>
       </c>
       <c r="P35">
-        <v>225.37231335</v>
+        <v>224.2671182999999</v>
       </c>
       <c r="Q35">
-        <v>237.37231335</v>
+        <v>236.2671182999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1205582139371696</v>
+        <v>0.1214841269163271</v>
       </c>
       <c r="T35">
-        <v>1.156485793646912</v>
+        <v>1.170809372958863</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.179419678824194</v>
+        <v>6.968260276505834</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09402602376477585</v>
+        <v>0.09383879419164805</v>
       </c>
       <c r="C36">
-        <v>1920.574147065</v>
+        <v>1903.831726523988</v>
       </c>
       <c r="D36">
-        <v>2667.266147065</v>
+        <v>2677.661726523988</v>
       </c>
       <c r="E36">
-        <v>-814.9079999999998</v>
+        <v>-787.7699999999998</v>
       </c>
       <c r="F36">
-        <v>922.6920000000001</v>
+        <v>949.8300000000002</v>
       </c>
       <c r="G36">
         <v>176</v>
@@ -4239,28 +4239,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M36">
-        <v>50.10217560000001</v>
+        <v>51.57576900000001</v>
       </c>
       <c r="N36">
-        <v>299.0228243999999</v>
+        <v>297.549231</v>
       </c>
       <c r="O36">
-        <v>74.75570609999998</v>
+        <v>74.38730774999999</v>
       </c>
       <c r="P36">
-        <v>224.2671182999999</v>
+        <v>223.16192325</v>
       </c>
       <c r="Q36">
-        <v>236.2671182999999</v>
+        <v>235.16192325</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1214841269163271</v>
+        <v>0.1224385295256124</v>
       </c>
       <c r="T36">
-        <v>1.170809372958863</v>
+        <v>1.185573677788105</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.968260276505834</v>
+        <v>6.769167125748526</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09383879419164805</v>
+        <v>0.09365156461852023</v>
       </c>
       <c r="C37">
-        <v>1903.831726523988</v>
+        <v>1887.170655879058</v>
       </c>
       <c r="D37">
-        <v>2677.661726523988</v>
+        <v>2688.138655879058</v>
       </c>
       <c r="E37">
-        <v>-787.7699999999998</v>
+        <v>-760.6319999999997</v>
       </c>
       <c r="F37">
-        <v>949.8300000000002</v>
+        <v>976.9680000000002</v>
       </c>
       <c r="G37">
         <v>176</v>
@@ -4321,28 +4321,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M37">
-        <v>51.57576900000001</v>
+        <v>53.04936240000001</v>
       </c>
       <c r="N37">
-        <v>297.549231</v>
+        <v>296.0756375999999</v>
       </c>
       <c r="O37">
-        <v>74.38730774999999</v>
+        <v>74.01890939999998</v>
       </c>
       <c r="P37">
-        <v>223.16192325</v>
+        <v>222.0567282</v>
       </c>
       <c r="Q37">
-        <v>235.16192325</v>
+        <v>234.0567282</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1224385295256124</v>
+        <v>0.1234227572164379</v>
       </c>
       <c r="T37">
-        <v>1.185573677788105</v>
+        <v>1.20079936714326</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.769167125748526</v>
+        <v>6.581134705588844</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09365156461852024</v>
+        <v>0.09346433504539245</v>
       </c>
       <c r="C38">
-        <v>1887.170655879057</v>
+        <v>1870.591893778196</v>
       </c>
       <c r="D38">
-        <v>2688.138655879057</v>
+        <v>2698.697893778196</v>
       </c>
       <c r="E38">
-        <v>-760.6319999999998</v>
+        <v>-733.4939999999998</v>
       </c>
       <c r="F38">
-        <v>976.9680000000001</v>
+        <v>1004.106</v>
       </c>
       <c r="G38">
         <v>176</v>
@@ -4403,28 +4403,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M38">
-        <v>53.04936240000001</v>
+        <v>54.52295580000001</v>
       </c>
       <c r="N38">
-        <v>296.0756375999999</v>
+        <v>294.6020441999999</v>
       </c>
       <c r="O38">
-        <v>74.01890939999998</v>
+        <v>73.65051104999998</v>
       </c>
       <c r="P38">
-        <v>222.0567282</v>
+        <v>220.9515331499999</v>
       </c>
       <c r="Q38">
-        <v>234.0567282</v>
+        <v>232.9515331499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1234227572164379</v>
+        <v>0.1244382302307817</v>
       </c>
       <c r="T38">
-        <v>1.20079936714326</v>
+        <v>1.216508411716039</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.581134705588844</v>
+        <v>6.403266200032388</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09346433504539245</v>
+        <v>0.09327710547226464</v>
       </c>
       <c r="C39">
-        <v>1870.591893778196</v>
+        <v>1854.0964139914</v>
       </c>
       <c r="D39">
-        <v>2698.697893778196</v>
+        <v>2709.3404139914</v>
       </c>
       <c r="E39">
-        <v>-733.4939999999998</v>
+        <v>-706.3559999999998</v>
       </c>
       <c r="F39">
-        <v>1004.106</v>
+        <v>1031.244</v>
       </c>
       <c r="G39">
         <v>176</v>
@@ -4485,28 +4485,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M39">
-        <v>54.52295580000001</v>
+        <v>55.99654920000001</v>
       </c>
       <c r="N39">
-        <v>294.6020441999999</v>
+        <v>293.1284507999999</v>
       </c>
       <c r="O39">
-        <v>73.65051104999998</v>
+        <v>73.28211269999998</v>
       </c>
       <c r="P39">
-        <v>220.9515331499999</v>
+        <v>219.8463381</v>
       </c>
       <c r="Q39">
-        <v>232.9515331499999</v>
+        <v>231.8463381</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1244382302307817</v>
+        <v>0.1254864604391365</v>
       </c>
       <c r="T39">
-        <v>1.216508411716039</v>
+        <v>1.232724199662134</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.403266200032388</v>
+        <v>6.234759194768379</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09327710547226464</v>
+        <v>0.09338237589913685</v>
       </c>
       <c r="C40">
-        <v>1854.0964139914</v>
+        <v>1820.964316039511</v>
       </c>
       <c r="D40">
-        <v>2709.3404139914</v>
+        <v>2703.346316039511</v>
       </c>
       <c r="E40">
-        <v>-706.3559999999998</v>
+        <v>-679.2179999999998</v>
       </c>
       <c r="F40">
-        <v>1031.244</v>
+        <v>1058.382</v>
       </c>
       <c r="G40">
         <v>176</v>
@@ -4567,45 +4567,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M40">
-        <v>55.99654920000001</v>
+        <v>58.5285246</v>
       </c>
       <c r="N40">
-        <v>293.1284507999999</v>
+        <v>290.5964753999999</v>
       </c>
       <c r="O40">
-        <v>73.28211269999998</v>
+        <v>72.64911884999998</v>
       </c>
       <c r="P40">
-        <v>219.8463381</v>
+        <v>217.9473565499999</v>
       </c>
       <c r="Q40">
-        <v>231.8463381</v>
+        <v>229.9473565499999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1254864604391365</v>
+        <v>0.126569058851044</v>
       </c>
       <c r="T40">
-        <v>1.232724199662134</v>
+        <v>1.24947165278679</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.234759194768379</v>
+        <v>5.965040164364572</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09338237589913685</v>
+        <v>0.09320264632600905</v>
       </c>
       <c r="C41">
-        <v>1820.964316039511</v>
+        <v>1804.07619272481</v>
       </c>
       <c r="D41">
-        <v>2703.346316039511</v>
+        <v>2713.59619272481</v>
       </c>
       <c r="E41">
-        <v>-679.2179999999998</v>
+        <v>-652.0799999999997</v>
       </c>
       <c r="F41">
-        <v>1058.382</v>
+        <v>1085.52</v>
       </c>
       <c r="G41">
         <v>176</v>
@@ -4649,28 +4649,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M41">
-        <v>58.5285246</v>
+        <v>60.02925600000001</v>
       </c>
       <c r="N41">
-        <v>290.5964753999999</v>
+        <v>289.0957439999999</v>
       </c>
       <c r="O41">
-        <v>72.64911884999998</v>
+        <v>72.27393599999998</v>
       </c>
       <c r="P41">
-        <v>217.9473565499999</v>
+        <v>216.8218079999999</v>
       </c>
       <c r="Q41">
-        <v>229.9473565499999</v>
+        <v>228.8218079999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.126569058851044</v>
+        <v>0.1276877438766817</v>
       </c>
       <c r="T41">
-        <v>1.24947165278679</v>
+        <v>1.266777354348934</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.965040164364572</v>
+        <v>5.815914160255457</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09320264632600905</v>
+        <v>0.09302291675288124</v>
       </c>
       <c r="C42">
-        <v>1804.07619272481</v>
+        <v>1787.266091103301</v>
       </c>
       <c r="D42">
-        <v>2713.59619272481</v>
+        <v>2723.924091103301</v>
       </c>
       <c r="E42">
-        <v>-652.0799999999997</v>
+        <v>-624.9419999999998</v>
       </c>
       <c r="F42">
-        <v>1085.52</v>
+        <v>1112.658</v>
       </c>
       <c r="G42">
         <v>176</v>
@@ -4731,28 +4731,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M42">
-        <v>60.02925600000001</v>
+        <v>61.52998740000001</v>
       </c>
       <c r="N42">
-        <v>289.0957439999999</v>
+        <v>287.5950125999999</v>
       </c>
       <c r="O42">
-        <v>72.27393599999998</v>
+        <v>71.89875314999998</v>
       </c>
       <c r="P42">
-        <v>216.8218079999999</v>
+        <v>215.6962594499999</v>
       </c>
       <c r="Q42">
-        <v>228.8218079999999</v>
+        <v>227.6962594499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1276877438766817</v>
+        <v>0.1288443504286123</v>
       </c>
       <c r="T42">
-        <v>1.266777354348934</v>
+        <v>1.284669689862337</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.815914160255457</v>
+        <v>5.674062595371177</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09302291675288124</v>
+        <v>0.09284318717975344</v>
       </c>
       <c r="C43">
-        <v>1787.266091103301</v>
+        <v>1770.534905425975</v>
       </c>
       <c r="D43">
-        <v>2723.924091103301</v>
+        <v>2734.330905425975</v>
       </c>
       <c r="E43">
-        <v>-624.9419999999998</v>
+        <v>-597.8039999999996</v>
       </c>
       <c r="F43">
-        <v>1112.658</v>
+        <v>1139.796</v>
       </c>
       <c r="G43">
         <v>176</v>
@@ -4813,28 +4813,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M43">
-        <v>61.52998740000001</v>
+        <v>63.03071880000002</v>
       </c>
       <c r="N43">
-        <v>287.5950125999999</v>
+        <v>286.0942812</v>
       </c>
       <c r="O43">
-        <v>71.89875314999998</v>
+        <v>71.52357029999999</v>
       </c>
       <c r="P43">
-        <v>215.6962594499999</v>
+        <v>214.5707109</v>
       </c>
       <c r="Q43">
-        <v>227.6962594499999</v>
+        <v>226.5707109</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1288443504286123</v>
+        <v>0.1300408399650921</v>
       </c>
       <c r="T43">
-        <v>1.284669689862337</v>
+        <v>1.303179002462409</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.674062595371177</v>
+        <v>5.538965866909959</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09284318717975346</v>
+        <v>0.09266345760662563</v>
       </c>
       <c r="C44">
-        <v>1770.534905425974</v>
+        <v>1753.883543662266</v>
       </c>
       <c r="D44">
-        <v>2734.330905425974</v>
+        <v>2744.817543662266</v>
       </c>
       <c r="E44">
-        <v>-597.8039999999999</v>
+        <v>-570.6659999999999</v>
       </c>
       <c r="F44">
-        <v>1139.796</v>
+        <v>1166.934</v>
       </c>
       <c r="G44">
         <v>176</v>
@@ -4895,28 +4895,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M44">
-        <v>63.0307188</v>
+        <v>64.53145019999999</v>
       </c>
       <c r="N44">
-        <v>286.0942812</v>
+        <v>284.5935497999999</v>
       </c>
       <c r="O44">
-        <v>71.52357029999999</v>
+        <v>71.14838744999999</v>
       </c>
       <c r="P44">
-        <v>214.5707109</v>
+        <v>213.44516235</v>
       </c>
       <c r="Q44">
-        <v>226.5707109</v>
+        <v>225.44516235</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1300408399650921</v>
+        <v>0.1312793115905713</v>
       </c>
       <c r="T44">
-        <v>1.303179002462409</v>
+        <v>1.322337764627395</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.538965866909961</v>
+        <v>5.41015270721438</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09266345760662563</v>
+        <v>0.09248372803349783</v>
       </c>
       <c r="C45">
-        <v>1753.883543662266</v>
+        <v>1737.312927764112</v>
       </c>
       <c r="D45">
-        <v>2744.817543662266</v>
+        <v>2755.384927764112</v>
       </c>
       <c r="E45">
-        <v>-570.6659999999999</v>
+        <v>-543.5279999999998</v>
       </c>
       <c r="F45">
-        <v>1166.934</v>
+        <v>1194.072</v>
       </c>
       <c r="G45">
         <v>176</v>
@@ -4977,28 +4977,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M45">
-        <v>64.53145019999999</v>
+        <v>66.03218160000002</v>
       </c>
       <c r="N45">
-        <v>284.5935497999999</v>
+        <v>283.0928183999999</v>
       </c>
       <c r="O45">
-        <v>71.14838744999999</v>
+        <v>70.77320459999999</v>
       </c>
       <c r="P45">
-        <v>213.44516235</v>
+        <v>212.3196138</v>
       </c>
       <c r="Q45">
-        <v>225.44516235</v>
+        <v>224.3196138</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1312793115905713</v>
+        <v>0.1325620143455318</v>
       </c>
       <c r="T45">
-        <v>1.322337764627395</v>
+        <v>1.342180768298275</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.41015270721438</v>
+        <v>5.287194691141325</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09248372803349783</v>
+        <v>0.09230399846037002</v>
       </c>
       <c r="C46">
-        <v>1737.312927764112</v>
+        <v>1720.823993936172</v>
       </c>
       <c r="D46">
-        <v>2755.384927764112</v>
+        <v>2766.033993936172</v>
       </c>
       <c r="E46">
-        <v>-543.5279999999998</v>
+        <v>-516.3899999999999</v>
       </c>
       <c r="F46">
-        <v>1194.072</v>
+        <v>1221.21</v>
       </c>
       <c r="G46">
         <v>176</v>
@@ -5059,28 +5059,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M46">
-        <v>66.03218160000002</v>
+        <v>67.53291300000001</v>
       </c>
       <c r="N46">
-        <v>283.0928183999999</v>
+        <v>281.5920869999999</v>
       </c>
       <c r="O46">
-        <v>70.77320459999999</v>
+        <v>70.39802174999998</v>
       </c>
       <c r="P46">
-        <v>212.3196138</v>
+        <v>211.1940652499999</v>
       </c>
       <c r="Q46">
-        <v>224.3196138</v>
+        <v>223.1940652499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1325620143455318</v>
+        <v>0.1338913608370364</v>
       </c>
       <c r="T46">
-        <v>1.342180768298275</v>
+        <v>1.362745335739004</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.287194691141325</v>
+        <v>5.169701475782629</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09230399846037002</v>
+        <v>0.09212426888724222</v>
       </c>
       <c r="C47">
-        <v>1720.823993936172</v>
+        <v>1704.4176929123</v>
       </c>
       <c r="D47">
-        <v>2766.033993936172</v>
+        <v>2776.7656929123</v>
       </c>
       <c r="E47">
-        <v>-516.3899999999999</v>
+        <v>-489.2519999999997</v>
       </c>
       <c r="F47">
-        <v>1221.21</v>
+        <v>1248.348</v>
       </c>
       <c r="G47">
         <v>176</v>
@@ -5141,28 +5141,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M47">
-        <v>67.53291300000001</v>
+        <v>69.03364440000001</v>
       </c>
       <c r="N47">
-        <v>281.5920869999999</v>
+        <v>280.0913555999999</v>
       </c>
       <c r="O47">
-        <v>70.39802174999998</v>
+        <v>70.02283889999998</v>
       </c>
       <c r="P47">
-        <v>211.1940652499999</v>
+        <v>210.0685166999999</v>
       </c>
       <c r="Q47">
-        <v>223.1940652499999</v>
+        <v>222.0685166999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1338913608370364</v>
+        <v>0.1352699423837819</v>
       </c>
       <c r="T47">
-        <v>1.362745335739004</v>
+        <v>1.384071553825686</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.169701475782629</v>
+        <v>5.057316661091702</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09212426888724222</v>
+        <v>0.09194453931411442</v>
       </c>
       <c r="C48">
-        <v>1704.4176929123</v>
+        <v>1688.094990238508</v>
       </c>
       <c r="D48">
-        <v>2776.7656929123</v>
+        <v>2787.580990238509</v>
       </c>
       <c r="E48">
-        <v>-489.2519999999997</v>
+        <v>-462.1139999999998</v>
       </c>
       <c r="F48">
-        <v>1248.348</v>
+        <v>1275.486</v>
       </c>
       <c r="G48">
         <v>176</v>
@@ -5223,28 +5223,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M48">
-        <v>69.03364440000001</v>
+        <v>70.53437580000001</v>
       </c>
       <c r="N48">
-        <v>280.0913555999999</v>
+        <v>278.5906241999999</v>
       </c>
       <c r="O48">
-        <v>70.02283889999998</v>
+        <v>69.64765604999998</v>
       </c>
       <c r="P48">
-        <v>210.0685166999999</v>
+        <v>208.94296815</v>
       </c>
       <c r="Q48">
-        <v>222.0685166999999</v>
+        <v>220.94296815</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1352699423837819</v>
+        <v>0.1367005458756876</v>
       </c>
       <c r="T48">
-        <v>1.384071553825686</v>
+        <v>1.406202534859036</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.057316661091702</v>
+        <v>4.949714178940815</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09194453931411442</v>
+        <v>0.09176480974098661</v>
       </c>
       <c r="C49">
-        <v>1688.094990238508</v>
+        <v>1671.856866562548</v>
       </c>
       <c r="D49">
-        <v>2787.580990238509</v>
+        <v>2798.480866562548</v>
       </c>
       <c r="E49">
-        <v>-462.1139999999998</v>
+        <v>-434.9759999999997</v>
       </c>
       <c r="F49">
-        <v>1275.486</v>
+        <v>1302.624</v>
       </c>
       <c r="G49">
         <v>176</v>
@@ -5305,28 +5305,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M49">
-        <v>70.53437580000001</v>
+        <v>72.03510720000001</v>
       </c>
       <c r="N49">
-        <v>278.5906241999999</v>
+        <v>277.0898927999999</v>
       </c>
       <c r="O49">
-        <v>69.64765604999998</v>
+        <v>69.27247319999998</v>
       </c>
       <c r="P49">
-        <v>208.94296815</v>
+        <v>207.8174195999999</v>
       </c>
       <c r="Q49">
-        <v>220.94296815</v>
+        <v>219.8174195999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1367005458756876</v>
+        <v>0.1381861725788204</v>
       </c>
       <c r="T49">
-        <v>1.406202534859036</v>
+        <v>1.429184707470592</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.949714178940815</v>
+        <v>4.846595133546215</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09176480974098661</v>
+        <v>0.09158508016785882</v>
       </c>
       <c r="C50">
-        <v>1671.856866562548</v>
+        <v>1655.70431793032</v>
       </c>
       <c r="D50">
-        <v>2798.480866562548</v>
+        <v>2809.46631793032</v>
       </c>
       <c r="E50">
-        <v>-434.9759999999999</v>
+        <v>-407.8379999999997</v>
       </c>
       <c r="F50">
-        <v>1302.624</v>
+        <v>1329.762</v>
       </c>
       <c r="G50">
         <v>176</v>
@@ -5387,28 +5387,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M50">
-        <v>72.0351072</v>
+        <v>73.53583860000001</v>
       </c>
       <c r="N50">
-        <v>277.0898927999999</v>
+        <v>275.5891614</v>
       </c>
       <c r="O50">
-        <v>69.27247319999998</v>
+        <v>68.89729034999999</v>
       </c>
       <c r="P50">
-        <v>207.8174195999999</v>
+        <v>206.69187105</v>
       </c>
       <c r="Q50">
-        <v>219.8174195999999</v>
+        <v>218.69187105</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1381861725788204</v>
+        <v>0.1397300591526643</v>
       </c>
       <c r="T50">
-        <v>1.429184707470592</v>
+        <v>1.453068141753188</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.846595133546215</v>
+        <v>4.747685028779966</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09158508016785882</v>
+        <v>0.09140535059473101</v>
       </c>
       <c r="C51">
-        <v>1655.70431793032</v>
+        <v>1639.638356089301</v>
       </c>
       <c r="D51">
-        <v>2809.46631793032</v>
+        <v>2820.538356089301</v>
       </c>
       <c r="E51">
-        <v>-407.8379999999997</v>
+        <v>-380.6999999999998</v>
       </c>
       <c r="F51">
-        <v>1329.762</v>
+        <v>1356.9</v>
       </c>
       <c r="G51">
         <v>176</v>
@@ -5469,28 +5469,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M51">
-        <v>73.53583860000001</v>
+        <v>75.03657000000001</v>
       </c>
       <c r="N51">
-        <v>275.5891614</v>
+        <v>274.0884299999999</v>
       </c>
       <c r="O51">
-        <v>68.89729034999999</v>
+        <v>68.52210749999998</v>
       </c>
       <c r="P51">
-        <v>206.69187105</v>
+        <v>205.5663224999999</v>
       </c>
       <c r="Q51">
-        <v>218.69187105</v>
+        <v>217.5663224999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1397300591526643</v>
+        <v>0.141335701189462</v>
       </c>
       <c r="T51">
-        <v>1.453068141753188</v>
+        <v>1.477906913407089</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.747685028779966</v>
+        <v>4.652731328204366</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09140535059473101</v>
+        <v>0.09122562102160321</v>
       </c>
       <c r="C52">
-        <v>1639.638356089301</v>
+        <v>1623.660008799155</v>
       </c>
       <c r="D52">
-        <v>2820.538356089301</v>
+        <v>2831.698008799155</v>
       </c>
       <c r="E52">
-        <v>-380.6999999999998</v>
+        <v>-353.5619999999999</v>
       </c>
       <c r="F52">
-        <v>1356.9</v>
+        <v>1384.038</v>
       </c>
       <c r="G52">
         <v>176</v>
@@ -5551,28 +5551,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M52">
-        <v>75.03657000000001</v>
+        <v>76.5373014</v>
       </c>
       <c r="N52">
-        <v>274.0884299999999</v>
+        <v>272.5876986</v>
       </c>
       <c r="O52">
-        <v>68.52210749999998</v>
+        <v>68.14692464999999</v>
       </c>
       <c r="P52">
-        <v>205.5663224999999</v>
+        <v>204.44077395</v>
       </c>
       <c r="Q52">
-        <v>217.5663224999999</v>
+        <v>216.44077395</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.141335701189462</v>
+        <v>0.1430068796359249</v>
       </c>
       <c r="T52">
-        <v>1.477906913407089</v>
+        <v>1.503759512475435</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.652731328204366</v>
+        <v>4.561501302161144</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09122562102160321</v>
+        <v>0.09202089144847539</v>
       </c>
       <c r="C53">
-        <v>1623.660008799155</v>
+        <v>1547.800194622525</v>
       </c>
       <c r="D53">
-        <v>2831.698008799155</v>
+        <v>2782.976194622525</v>
       </c>
       <c r="E53">
-        <v>-353.5619999999999</v>
+        <v>-326.4239999999998</v>
       </c>
       <c r="F53">
-        <v>1384.038</v>
+        <v>1411.176</v>
       </c>
       <c r="G53">
         <v>176</v>
@@ -5633,45 +5633,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M53">
-        <v>76.5373014</v>
+        <v>81.56597280000001</v>
       </c>
       <c r="N53">
-        <v>272.5876986</v>
+        <v>267.5590271999999</v>
       </c>
       <c r="O53">
-        <v>68.14692464999999</v>
+        <v>66.88975679999999</v>
       </c>
       <c r="P53">
-        <v>204.44077395</v>
+        <v>200.6692704</v>
       </c>
       <c r="Q53">
-        <v>216.44077395</v>
+        <v>212.6692704</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1430068796359249</v>
+        <v>0.1447476905176571</v>
       </c>
       <c r="T53">
-        <v>1.503759512475435</v>
+        <v>1.530689303171628</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.561501302161144</v>
+        <v>4.280277522785824</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09202089144847539</v>
+        <v>0.0918599118753476</v>
       </c>
       <c r="C54">
-        <v>1547.800194622525</v>
+        <v>1530.388707366352</v>
       </c>
       <c r="D54">
-        <v>2782.976194622525</v>
+        <v>2792.702707366353</v>
       </c>
       <c r="E54">
-        <v>-326.4239999999998</v>
+        <v>-299.2859999999998</v>
       </c>
       <c r="F54">
-        <v>1411.176</v>
+        <v>1438.314</v>
       </c>
       <c r="G54">
         <v>176</v>
@@ -5715,28 +5715,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M54">
-        <v>81.56597280000001</v>
+        <v>83.13454920000001</v>
       </c>
       <c r="N54">
-        <v>267.5590271999999</v>
+        <v>265.9904508</v>
       </c>
       <c r="O54">
-        <v>66.88975679999999</v>
+        <v>66.49761269999999</v>
       </c>
       <c r="P54">
-        <v>200.6692704</v>
+        <v>199.4928381</v>
       </c>
       <c r="Q54">
-        <v>212.6692704</v>
+        <v>211.4928381</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1447476905176571</v>
+        <v>0.1465625784581864</v>
       </c>
       <c r="T54">
-        <v>1.530689303171628</v>
+        <v>1.558765042408085</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.280277522785824</v>
+        <v>4.199517569525714</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0918599118753476</v>
+        <v>0.09169893230221979</v>
       </c>
       <c r="C55">
-        <v>1530.388707366352</v>
+        <v>1513.045446963878</v>
       </c>
       <c r="D55">
-        <v>2792.702707366353</v>
+        <v>2802.497446963879</v>
       </c>
       <c r="E55">
-        <v>-299.2859999999998</v>
+        <v>-272.1479999999997</v>
       </c>
       <c r="F55">
-        <v>1438.314</v>
+        <v>1465.452</v>
       </c>
       <c r="G55">
         <v>176</v>
@@ -5797,28 +5797,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M55">
-        <v>83.13454920000001</v>
+        <v>84.70312560000002</v>
       </c>
       <c r="N55">
-        <v>265.9904508</v>
+        <v>264.4218743999999</v>
       </c>
       <c r="O55">
-        <v>66.49761269999999</v>
+        <v>66.10546859999998</v>
       </c>
       <c r="P55">
-        <v>199.4928381</v>
+        <v>198.3164057999999</v>
       </c>
       <c r="Q55">
-        <v>211.4928381</v>
+        <v>210.3164057999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1465625784581864</v>
+        <v>0.148456374570043</v>
       </c>
       <c r="T55">
-        <v>1.558765042408085</v>
+        <v>1.58806146595917</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.199517569525714</v>
+        <v>4.121748725645608</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09169893230221979</v>
+        <v>0.091537952729092</v>
       </c>
       <c r="C56">
-        <v>1513.045446963878</v>
+        <v>1495.771133810033</v>
       </c>
       <c r="D56">
-        <v>2802.497446963879</v>
+        <v>2812.361133810033</v>
       </c>
       <c r="E56">
-        <v>-272.1479999999997</v>
+        <v>-245.0099999999998</v>
       </c>
       <c r="F56">
-        <v>1465.452</v>
+        <v>1492.59</v>
       </c>
       <c r="G56">
         <v>176</v>
@@ -5879,28 +5879,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M56">
-        <v>84.70312560000002</v>
+        <v>86.27170200000002</v>
       </c>
       <c r="N56">
-        <v>264.4218743999999</v>
+        <v>262.8532979999999</v>
       </c>
       <c r="O56">
-        <v>66.10546859999998</v>
+        <v>65.71332449999998</v>
       </c>
       <c r="P56">
-        <v>198.3164057999999</v>
+        <v>197.1399734999999</v>
       </c>
       <c r="Q56">
-        <v>210.3164057999999</v>
+        <v>209.1399734999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.148456374570043</v>
+        <v>0.1504343393979822</v>
       </c>
       <c r="T56">
-        <v>1.58806146595917</v>
+        <v>1.618659952779193</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.121748725645608</v>
+        <v>4.046807839724779</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.091537952729092</v>
+        <v>0.09284697315596419</v>
       </c>
       <c r="C57">
-        <v>1495.771133810033</v>
+        <v>1390.382867641059</v>
       </c>
       <c r="D57">
-        <v>2812.361133810033</v>
+        <v>2734.110867641059</v>
       </c>
       <c r="E57">
-        <v>-245.0099999999998</v>
+        <v>-217.8719999999996</v>
       </c>
       <c r="F57">
-        <v>1492.59</v>
+        <v>1519.728</v>
       </c>
       <c r="G57">
         <v>176</v>
@@ -5961,45 +5961,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M57">
-        <v>86.27170200000002</v>
+        <v>93.15932640000001</v>
       </c>
       <c r="N57">
-        <v>262.8532979999999</v>
+        <v>255.9656735999999</v>
       </c>
       <c r="O57">
-        <v>65.71332449999998</v>
+        <v>63.99141839999999</v>
       </c>
       <c r="P57">
-        <v>197.1399734999999</v>
+        <v>191.9742552</v>
       </c>
       <c r="Q57">
-        <v>209.1399734999999</v>
+        <v>203.9742552</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1504343393979822</v>
+        <v>0.1525022117181004</v>
       </c>
       <c r="T57">
-        <v>1.618659952779193</v>
+        <v>1.650649279909217</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.046807839724779</v>
+        <v>3.747611897717628</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09284697315596419</v>
+        <v>0.09271224358283639</v>
       </c>
       <c r="C58">
-        <v>1390.382867641059</v>
+        <v>1371.09709473463</v>
       </c>
       <c r="D58">
-        <v>2734.110867641059</v>
+        <v>2741.96309473463</v>
       </c>
       <c r="E58">
-        <v>-217.8719999999996</v>
+        <v>-190.7339999999997</v>
       </c>
       <c r="F58">
-        <v>1519.728</v>
+        <v>1546.866</v>
       </c>
       <c r="G58">
         <v>176</v>
@@ -6043,28 +6043,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M58">
-        <v>93.15932640000001</v>
+        <v>94.82288580000001</v>
       </c>
       <c r="N58">
-        <v>255.9656735999999</v>
+        <v>254.3021141999999</v>
       </c>
       <c r="O58">
-        <v>63.99141839999999</v>
+        <v>63.57552854999999</v>
       </c>
       <c r="P58">
-        <v>191.9742552</v>
+        <v>190.7265856499999</v>
       </c>
       <c r="Q58">
-        <v>203.9742552</v>
+        <v>202.7265856499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1525022117181004</v>
+        <v>0.1546662641461312</v>
       </c>
       <c r="T58">
-        <v>1.650649279909217</v>
+        <v>1.684126482719706</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.747611897717628</v>
+        <v>3.681864320564687</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09271224358283639</v>
+        <v>0.09257751400970859</v>
       </c>
       <c r="C59">
-        <v>1371.09709473463</v>
+        <v>1351.856554125248</v>
       </c>
       <c r="D59">
-        <v>2741.96309473463</v>
+        <v>2749.860554125249</v>
       </c>
       <c r="E59">
-        <v>-190.7339999999997</v>
+        <v>-163.5959999999995</v>
       </c>
       <c r="F59">
-        <v>1546.866</v>
+        <v>1574.004</v>
       </c>
       <c r="G59">
         <v>176</v>
@@ -6125,28 +6125,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M59">
-        <v>94.82288580000001</v>
+        <v>96.48644520000002</v>
       </c>
       <c r="N59">
-        <v>254.3021141999999</v>
+        <v>252.6385547999999</v>
       </c>
       <c r="O59">
-        <v>63.57552854999999</v>
+        <v>63.15963869999998</v>
       </c>
       <c r="P59">
-        <v>190.7265856499999</v>
+        <v>189.4789160999999</v>
       </c>
       <c r="Q59">
-        <v>202.7265856499999</v>
+        <v>201.4789160999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1546662641461312</v>
+        <v>0.1569333666897824</v>
       </c>
       <c r="T59">
-        <v>1.684126482719706</v>
+        <v>1.719197838044981</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.681864320564687</v>
+        <v>3.618383901244606</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09257751400970858</v>
+        <v>0.09244278443658079</v>
       </c>
       <c r="C60">
-        <v>1351.85655412525</v>
+        <v>1332.661637778885</v>
       </c>
       <c r="D60">
-        <v>2749.86055412525</v>
+        <v>2757.803637778885</v>
       </c>
       <c r="E60">
-        <v>-163.596</v>
+        <v>-136.4579999999999</v>
       </c>
       <c r="F60">
-        <v>1574.004</v>
+        <v>1601.142</v>
       </c>
       <c r="G60">
         <v>176</v>
@@ -6207,28 +6207,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M60">
-        <v>96.48644519999999</v>
+        <v>98.1500046</v>
       </c>
       <c r="N60">
-        <v>252.6385548</v>
+        <v>250.9749954</v>
       </c>
       <c r="O60">
-        <v>63.15963869999999</v>
+        <v>62.74374884999999</v>
       </c>
       <c r="P60">
-        <v>189.4789161</v>
+        <v>188.23124655</v>
       </c>
       <c r="Q60">
-        <v>201.4789161</v>
+        <v>200.23124655</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1569333666897823</v>
+        <v>0.1593110596014165</v>
       </c>
       <c r="T60">
-        <v>1.719197838044981</v>
+        <v>1.755979991191001</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.618383901244607</v>
+        <v>3.557055360545545</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09244278443658079</v>
+        <v>0.09356805486345299</v>
       </c>
       <c r="C61">
-        <v>1332.661637778885</v>
+        <v>1240.558152255474</v>
       </c>
       <c r="D61">
-        <v>2757.803637778885</v>
+        <v>2692.838152255474</v>
       </c>
       <c r="E61">
-        <v>-136.4579999999999</v>
+        <v>-109.3199999999999</v>
       </c>
       <c r="F61">
-        <v>1601.142</v>
+        <v>1628.28</v>
       </c>
       <c r="G61">
         <v>176</v>
@@ -6289,45 +6289,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M61">
-        <v>98.1500046</v>
+        <v>104.372748</v>
       </c>
       <c r="N61">
-        <v>250.9749954</v>
+        <v>244.7522519999999</v>
       </c>
       <c r="O61">
-        <v>62.74374884999999</v>
+        <v>61.18806299999999</v>
       </c>
       <c r="P61">
-        <v>188.23124655</v>
+        <v>183.5641889999999</v>
       </c>
       <c r="Q61">
-        <v>200.23124655</v>
+        <v>195.5641889999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1593110596014165</v>
+        <v>0.1618076371586324</v>
       </c>
       <c r="T61">
-        <v>1.755979991191001</v>
+        <v>1.794601251994322</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.557055360545545</v>
+        <v>3.344982351140165</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09356805486345299</v>
+        <v>0.09345432529032519</v>
       </c>
       <c r="C62">
-        <v>1240.558152255474</v>
+        <v>1219.846753234346</v>
       </c>
       <c r="D62">
-        <v>2692.838152255474</v>
+        <v>2699.264753234346</v>
       </c>
       <c r="E62">
-        <v>-109.3199999999999</v>
+        <v>-82.18199999999979</v>
       </c>
       <c r="F62">
-        <v>1628.28</v>
+        <v>1655.418</v>
       </c>
       <c r="G62">
         <v>176</v>
@@ -6371,28 +6371,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M62">
-        <v>104.372748</v>
+        <v>106.1122938</v>
       </c>
       <c r="N62">
-        <v>244.7522519999999</v>
+        <v>243.0127061999999</v>
       </c>
       <c r="O62">
-        <v>61.18806299999999</v>
+        <v>60.75317654999998</v>
       </c>
       <c r="P62">
-        <v>183.5641889999999</v>
+        <v>182.2595296499999</v>
       </c>
       <c r="Q62">
-        <v>195.5641889999999</v>
+        <v>194.2595296499999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1618076371586324</v>
+        <v>0.1644322443341671</v>
       </c>
       <c r="T62">
-        <v>1.794601251994322</v>
+        <v>1.835203090274737</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.344982351140165</v>
+        <v>3.290146574891965</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09345432529032519</v>
+        <v>0.09334059571719738</v>
       </c>
       <c r="C63">
-        <v>1219.846753234346</v>
+        <v>1199.166102443228</v>
       </c>
       <c r="D63">
-        <v>2699.264753234346</v>
+        <v>2705.722102443228</v>
       </c>
       <c r="E63">
-        <v>-82.18199999999979</v>
+        <v>-55.04399999999987</v>
       </c>
       <c r="F63">
-        <v>1655.418</v>
+        <v>1682.556</v>
       </c>
       <c r="G63">
         <v>176</v>
@@ -6453,28 +6453,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M63">
-        <v>106.1122938</v>
+        <v>107.8518396</v>
       </c>
       <c r="N63">
-        <v>243.0127061999999</v>
+        <v>241.2731603999999</v>
       </c>
       <c r="O63">
-        <v>60.75317654999998</v>
+        <v>60.31829009999998</v>
       </c>
       <c r="P63">
-        <v>182.2595296499999</v>
+        <v>180.9548703</v>
       </c>
       <c r="Q63">
-        <v>194.2595296499999</v>
+        <v>192.9548703</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1644322443341671</v>
+        <v>0.1671949887294668</v>
       </c>
       <c r="T63">
-        <v>1.835203090274737</v>
+        <v>1.877941867412016</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.290146574891965</v>
+        <v>3.237079694651772</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09334059571719738</v>
+        <v>0.09322686614406958</v>
       </c>
       <c r="C64">
-        <v>1199.166102443228</v>
+        <v>1178.516421084788</v>
       </c>
       <c r="D64">
-        <v>2705.722102443228</v>
+        <v>2712.210421084788</v>
       </c>
       <c r="E64">
-        <v>-55.04399999999987</v>
+        <v>-27.90599999999972</v>
       </c>
       <c r="F64">
-        <v>1682.556</v>
+        <v>1709.694</v>
       </c>
       <c r="G64">
         <v>176</v>
@@ -6535,28 +6535,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M64">
-        <v>107.8518396</v>
+        <v>109.5913854</v>
       </c>
       <c r="N64">
-        <v>241.2731603999999</v>
+        <v>239.5336145999999</v>
       </c>
       <c r="O64">
-        <v>60.31829009999998</v>
+        <v>59.88340364999998</v>
       </c>
       <c r="P64">
-        <v>180.9548703</v>
+        <v>179.6502109499999</v>
       </c>
       <c r="Q64">
-        <v>192.9548703</v>
+        <v>191.6502109499999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1671949887294668</v>
+        <v>0.1701070706596475</v>
       </c>
       <c r="T64">
-        <v>1.877941867412016</v>
+        <v>1.922990848718877</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.237079694651772</v>
+        <v>3.185697477276347</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09322686614406958</v>
+        <v>0.09311313657094178</v>
       </c>
       <c r="C65">
-        <v>1178.516421084788</v>
+        <v>1157.897932488567</v>
       </c>
       <c r="D65">
-        <v>2712.210421084788</v>
+        <v>2718.729932488567</v>
       </c>
       <c r="E65">
-        <v>-27.90599999999972</v>
+        <v>-0.7679999999998017</v>
       </c>
       <c r="F65">
-        <v>1709.694</v>
+        <v>1736.832</v>
       </c>
       <c r="G65">
         <v>176</v>
@@ -6617,28 +6617,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M65">
-        <v>109.5913854</v>
+        <v>111.3309312</v>
       </c>
       <c r="N65">
-        <v>239.5336145999999</v>
+        <v>237.7940687999999</v>
       </c>
       <c r="O65">
-        <v>59.88340364999998</v>
+        <v>59.44851719999998</v>
       </c>
       <c r="P65">
-        <v>179.6502109499999</v>
+        <v>178.3455516</v>
       </c>
       <c r="Q65">
-        <v>191.6502109499999</v>
+        <v>190.3455516</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1701070706596475</v>
+        <v>0.1731809349192827</v>
       </c>
       <c r="T65">
-        <v>1.922990848718877</v>
+        <v>1.970542551209452</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.185697477276347</v>
+        <v>3.135920954193904</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09311313657094178</v>
+        <v>0.09299940699781398</v>
       </c>
       <c r="C66">
-        <v>1157.897932488567</v>
+        <v>1137.310862136602</v>
       </c>
       <c r="D66">
-        <v>2718.729932488567</v>
+        <v>2725.280862136603</v>
       </c>
       <c r="E66">
-        <v>-0.7679999999998017</v>
+        <v>26.37000000000035</v>
       </c>
       <c r="F66">
-        <v>1736.832</v>
+        <v>1763.97</v>
       </c>
       <c r="G66">
         <v>176</v>
@@ -6699,28 +6699,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M66">
-        <v>111.3309312</v>
+        <v>113.070477</v>
       </c>
       <c r="N66">
-        <v>237.7940687999999</v>
+        <v>236.0545229999999</v>
       </c>
       <c r="O66">
-        <v>59.44851719999998</v>
+        <v>59.01363074999998</v>
       </c>
       <c r="P66">
-        <v>178.3455516</v>
+        <v>177.0408922499999</v>
       </c>
       <c r="Q66">
-        <v>190.3455516</v>
+        <v>189.0408922499999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1731809349192827</v>
+        <v>0.1764304485651828</v>
       </c>
       <c r="T66">
-        <v>1.970542551209452</v>
+        <v>2.020811493842347</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.135920954193904</v>
+        <v>3.087676016437074</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09299940699781398</v>
+        <v>0.09288567742468617</v>
       </c>
       <c r="C67">
-        <v>1137.310862136602</v>
+        <v>1116.755437689432</v>
       </c>
       <c r="D67">
-        <v>2725.280862136603</v>
+        <v>2731.863437689432</v>
       </c>
       <c r="E67">
-        <v>26.37000000000035</v>
+        <v>53.50800000000027</v>
       </c>
       <c r="F67">
-        <v>1763.97</v>
+        <v>1791.108</v>
       </c>
       <c r="G67">
         <v>176</v>
@@ -6781,28 +6781,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M67">
-        <v>113.070477</v>
+        <v>114.8100228</v>
       </c>
       <c r="N67">
-        <v>236.0545229999999</v>
+        <v>234.3149771999999</v>
       </c>
       <c r="O67">
-        <v>59.01363074999998</v>
+        <v>58.57874429999998</v>
       </c>
       <c r="P67">
-        <v>177.0408922499999</v>
+        <v>175.7362328999999</v>
       </c>
       <c r="Q67">
-        <v>189.0408922499999</v>
+        <v>187.7362328999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1764304485651828</v>
+        <v>0.1798711100726064</v>
       </c>
       <c r="T67">
-        <v>2.020811493842347</v>
+        <v>2.074037433100705</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.087676016437074</v>
+        <v>3.040893046491059</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09288567742468617</v>
+        <v>0.09669144785155837</v>
       </c>
       <c r="C68">
-        <v>1116.755437689432</v>
+        <v>885.3228946900333</v>
       </c>
       <c r="D68">
-        <v>2731.863437689432</v>
+        <v>2527.568894690034</v>
       </c>
       <c r="E68">
-        <v>53.50800000000027</v>
+        <v>80.64600000000041</v>
       </c>
       <c r="F68">
-        <v>1791.108</v>
+        <v>1818.246</v>
       </c>
       <c r="G68">
         <v>176</v>
@@ -6863,45 +6863,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M68">
-        <v>114.8100228</v>
+        <v>130.7318874</v>
       </c>
       <c r="N68">
-        <v>234.3149771999999</v>
+        <v>218.3931125999999</v>
       </c>
       <c r="O68">
-        <v>58.57874429999998</v>
+        <v>54.59827814999998</v>
       </c>
       <c r="P68">
-        <v>175.7362328999999</v>
+        <v>163.7948344499999</v>
       </c>
       <c r="Q68">
-        <v>187.7362328999999</v>
+        <v>175.7948344499999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1798711100726064</v>
+        <v>0.1835202965198738</v>
       </c>
       <c r="T68">
-        <v>2.074037433100705</v>
+        <v>2.13048918685957</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.040893046491059</v>
+        <v>2.670542030283576</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09669144785155837</v>
+        <v>0.09663621827843055</v>
       </c>
       <c r="C69">
-        <v>885.3228946900333</v>
+        <v>860.9309005069942</v>
       </c>
       <c r="D69">
-        <v>2527.568894690034</v>
+        <v>2530.314900506994</v>
       </c>
       <c r="E69">
-        <v>80.64600000000041</v>
+        <v>107.7840000000003</v>
       </c>
       <c r="F69">
-        <v>1818.246</v>
+        <v>1845.384</v>
       </c>
       <c r="G69">
         <v>176</v>
@@ -6945,28 +6945,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M69">
-        <v>130.7318874</v>
+        <v>132.6831096</v>
       </c>
       <c r="N69">
-        <v>218.3931125999999</v>
+        <v>216.4418903999999</v>
       </c>
       <c r="O69">
-        <v>54.59827814999998</v>
+        <v>54.11047259999998</v>
       </c>
       <c r="P69">
-        <v>163.7948344499999</v>
+        <v>162.3314177999999</v>
       </c>
       <c r="Q69">
-        <v>175.7948344499999</v>
+        <v>174.3314177999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1835202965198738</v>
+        <v>0.1873975571200955</v>
       </c>
       <c r="T69">
-        <v>2.13048918685957</v>
+        <v>2.190469175228364</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.670542030283576</v>
+        <v>2.631269353367641</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09663621827843055</v>
+        <v>0.09658098870530277</v>
       </c>
       <c r="C70">
-        <v>860.9309005069942</v>
+        <v>836.5448794541721</v>
       </c>
       <c r="D70">
-        <v>2530.314900506994</v>
+        <v>2533.066879454173</v>
       </c>
       <c r="E70">
-        <v>107.7840000000003</v>
+        <v>134.9220000000005</v>
       </c>
       <c r="F70">
-        <v>1845.384</v>
+        <v>1872.522</v>
       </c>
       <c r="G70">
         <v>176</v>
@@ -7027,28 +7027,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M70">
-        <v>132.6831096</v>
+        <v>134.6343318</v>
       </c>
       <c r="N70">
-        <v>216.4418903999999</v>
+        <v>214.4906681999999</v>
       </c>
       <c r="O70">
-        <v>54.11047259999998</v>
+        <v>53.62266704999998</v>
       </c>
       <c r="P70">
-        <v>162.3314177999999</v>
+        <v>160.8680011499999</v>
       </c>
       <c r="Q70">
-        <v>174.3314177999999</v>
+        <v>172.8680011499999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1873975571200955</v>
+        <v>0.1915249635654928</v>
       </c>
       <c r="T70">
-        <v>2.190469175228364</v>
+        <v>2.254318840266113</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.631269353367641</v>
+        <v>2.593135014913037</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09658098870530277</v>
+        <v>0.09652575913217495</v>
       </c>
       <c r="C71">
-        <v>836.5448794541721</v>
+        <v>812.1648510419786</v>
       </c>
       <c r="D71">
-        <v>2533.066879454173</v>
+        <v>2535.824851041979</v>
       </c>
       <c r="E71">
-        <v>134.9220000000005</v>
+        <v>162.0600000000004</v>
       </c>
       <c r="F71">
-        <v>1872.522</v>
+        <v>1899.66</v>
       </c>
       <c r="G71">
         <v>176</v>
@@ -7109,28 +7109,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M71">
-        <v>134.6343318</v>
+        <v>136.585554</v>
       </c>
       <c r="N71">
-        <v>214.4906681999999</v>
+        <v>212.5394459999999</v>
       </c>
       <c r="O71">
-        <v>53.62266704999998</v>
+        <v>53.13486149999998</v>
       </c>
       <c r="P71">
-        <v>160.8680011499999</v>
+        <v>159.4045844999999</v>
       </c>
       <c r="Q71">
-        <v>172.8680011499999</v>
+        <v>171.4045844999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1915249635654928</v>
+        <v>0.1959275304405832</v>
       </c>
       <c r="T71">
-        <v>2.254318840266113</v>
+        <v>2.322425149639712</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.593135014913037</v>
+        <v>2.556090228985709</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09652575913217495</v>
+        <v>0.09647052955904716</v>
       </c>
       <c r="C72">
-        <v>812.1648510419786</v>
+        <v>787.7908348658834</v>
       </c>
       <c r="D72">
-        <v>2535.824851041979</v>
+        <v>2538.588834865884</v>
       </c>
       <c r="E72">
-        <v>162.0600000000004</v>
+        <v>189.1980000000003</v>
       </c>
       <c r="F72">
-        <v>1899.66</v>
+        <v>1926.798</v>
       </c>
       <c r="G72">
         <v>176</v>
@@ -7191,28 +7191,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M72">
-        <v>136.585554</v>
+        <v>138.5367762</v>
       </c>
       <c r="N72">
-        <v>212.5394459999999</v>
+        <v>210.5882237999999</v>
       </c>
       <c r="O72">
-        <v>53.13486149999998</v>
+        <v>52.64705594999998</v>
       </c>
       <c r="P72">
-        <v>159.4045844999999</v>
+        <v>157.9411678499999</v>
       </c>
       <c r="Q72">
-        <v>171.4045844999999</v>
+        <v>169.9411678499999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1959275304405832</v>
+        <v>0.200633722617404</v>
       </c>
       <c r="T72">
-        <v>2.322425149639712</v>
+        <v>2.395228445866663</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.556090228985709</v>
+        <v>2.520088958154924</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09647052955904717</v>
+        <v>0.09852129998591935</v>
       </c>
       <c r="C73">
-        <v>787.7908348658832</v>
+        <v>661.9059733522013</v>
       </c>
       <c r="D73">
-        <v>2538.588834865883</v>
+        <v>2439.841973352201</v>
       </c>
       <c r="E73">
-        <v>189.1980000000001</v>
+        <v>216.3360000000002</v>
       </c>
       <c r="F73">
-        <v>1926.798</v>
+        <v>1953.936</v>
       </c>
       <c r="G73">
         <v>176</v>
@@ -7273,45 +7273,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M73">
-        <v>138.5367762</v>
+        <v>148.1083488</v>
       </c>
       <c r="N73">
-        <v>210.5882237999999</v>
+        <v>201.0166511999999</v>
       </c>
       <c r="O73">
-        <v>52.64705594999998</v>
+        <v>50.25416279999998</v>
       </c>
       <c r="P73">
-        <v>157.9411678499999</v>
+        <v>150.7624883999999</v>
       </c>
       <c r="Q73">
-        <v>169.9411678499999</v>
+        <v>162.7624883999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.200633722617404</v>
+        <v>0.2056760713782834</v>
       </c>
       <c r="T73">
-        <v>2.395228445866662</v>
+        <v>2.473231977538394</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.520088958154924</v>
+        <v>2.357227008664078</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09852129998591935</v>
+        <v>0.09849532041279155</v>
       </c>
       <c r="C74">
-        <v>661.9059733522013</v>
+        <v>635.970851567391</v>
       </c>
       <c r="D74">
-        <v>2439.841973352201</v>
+        <v>2441.044851567391</v>
       </c>
       <c r="E74">
-        <v>216.3360000000002</v>
+        <v>243.4740000000002</v>
       </c>
       <c r="F74">
-        <v>1953.936</v>
+        <v>1981.074</v>
       </c>
       <c r="G74">
         <v>176</v>
@@ -7355,28 +7355,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M74">
-        <v>148.1083488</v>
+        <v>150.1654092</v>
       </c>
       <c r="N74">
-        <v>201.0166511999999</v>
+        <v>198.9595907999999</v>
       </c>
       <c r="O74">
-        <v>50.25416279999998</v>
+        <v>49.73989769999998</v>
       </c>
       <c r="P74">
-        <v>150.7624883999999</v>
+        <v>149.2196930999999</v>
       </c>
       <c r="Q74">
-        <v>162.7624883999999</v>
+        <v>161.2196930999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2056760713782834</v>
+        <v>0.2110919274547835</v>
       </c>
       <c r="T74">
-        <v>2.473231977538394</v>
+        <v>2.557013548593218</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.357227008664078</v>
+        <v>2.324936227723474</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09849532041279155</v>
+        <v>0.09846934083966374</v>
       </c>
       <c r="C75">
-        <v>635.970851567391</v>
+        <v>610.0369164411588</v>
       </c>
       <c r="D75">
-        <v>2441.044851567391</v>
+        <v>2442.248916441159</v>
       </c>
       <c r="E75">
-        <v>243.4740000000002</v>
+        <v>270.6120000000003</v>
       </c>
       <c r="F75">
-        <v>1981.074</v>
+        <v>2008.212</v>
       </c>
       <c r="G75">
         <v>176</v>
@@ -7437,28 +7437,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M75">
-        <v>150.1654092</v>
+        <v>152.2224696</v>
       </c>
       <c r="N75">
-        <v>198.9595907999999</v>
+        <v>196.9025303999999</v>
       </c>
       <c r="O75">
-        <v>49.73989769999998</v>
+        <v>49.22563259999998</v>
       </c>
       <c r="P75">
-        <v>149.2196930999999</v>
+        <v>147.6768977999999</v>
       </c>
       <c r="Q75">
-        <v>161.2196930999999</v>
+        <v>159.6768977999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2110919274547835</v>
+        <v>0.2169243878448605</v>
       </c>
       <c r="T75">
-        <v>2.557013548593218</v>
+        <v>2.647239855883027</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.324936227723474</v>
+        <v>2.293518170592076</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09846934083966374</v>
+        <v>0.09844336126653594</v>
       </c>
       <c r="C76">
-        <v>610.0369164411588</v>
+        <v>584.1041697303579</v>
       </c>
       <c r="D76">
-        <v>2442.248916441159</v>
+        <v>2443.454169730358</v>
       </c>
       <c r="E76">
-        <v>270.6120000000003</v>
+        <v>297.7500000000002</v>
       </c>
       <c r="F76">
-        <v>2008.212</v>
+        <v>2035.35</v>
       </c>
       <c r="G76">
         <v>176</v>
@@ -7519,28 +7519,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M76">
-        <v>152.2224696</v>
+        <v>154.27953</v>
       </c>
       <c r="N76">
-        <v>196.9025303999999</v>
+        <v>194.8454699999999</v>
       </c>
       <c r="O76">
-        <v>49.22563259999998</v>
+        <v>48.71136749999998</v>
       </c>
       <c r="P76">
-        <v>147.6768977999999</v>
+        <v>146.1341024999999</v>
       </c>
       <c r="Q76">
-        <v>159.6768977999999</v>
+        <v>158.1341024999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2169243878448605</v>
+        <v>0.2232234450661437</v>
       </c>
       <c r="T76">
-        <v>2.647239855883027</v>
+        <v>2.744684267756023</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.293518170592076</v>
+        <v>2.262937928317515</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09844336126653594</v>
+        <v>0.09841738169340813</v>
       </c>
       <c r="C77">
-        <v>584.1041697303579</v>
+        <v>558.1726131953105</v>
       </c>
       <c r="D77">
-        <v>2443.454169730358</v>
+        <v>2444.660613195311</v>
       </c>
       <c r="E77">
-        <v>297.7500000000002</v>
+        <v>324.8880000000004</v>
       </c>
       <c r="F77">
-        <v>2035.35</v>
+        <v>2062.488</v>
       </c>
       <c r="G77">
         <v>176</v>
@@ -7601,28 +7601,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M77">
-        <v>154.27953</v>
+        <v>156.3365904</v>
       </c>
       <c r="N77">
-        <v>194.8454699999999</v>
+        <v>192.7884095999999</v>
       </c>
       <c r="O77">
-        <v>48.71136749999998</v>
+        <v>48.19710239999998</v>
       </c>
       <c r="P77">
-        <v>146.1341024999999</v>
+        <v>144.5913071999999</v>
       </c>
       <c r="Q77">
-        <v>158.1341024999999</v>
+        <v>156.5913071999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2232234450661437</v>
+        <v>0.2300474237225339</v>
       </c>
       <c r="T77">
-        <v>2.744684267756023</v>
+        <v>2.850249047285101</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.262937928317515</v>
+        <v>2.233162429260705</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09841738169340813</v>
+        <v>0.09839140212028034</v>
       </c>
       <c r="C78">
-        <v>558.1726131953105</v>
+        <v>532.2422485998181</v>
       </c>
       <c r="D78">
-        <v>2444.660613195311</v>
+        <v>2445.868248599818</v>
       </c>
       <c r="E78">
-        <v>324.8880000000004</v>
+        <v>352.0260000000003</v>
       </c>
       <c r="F78">
-        <v>2062.488</v>
+        <v>2089.626</v>
       </c>
       <c r="G78">
         <v>176</v>
@@ -7683,28 +7683,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M78">
-        <v>156.3365904</v>
+        <v>158.3936508</v>
       </c>
       <c r="N78">
-        <v>192.7884095999999</v>
+        <v>190.7313491999999</v>
       </c>
       <c r="O78">
-        <v>48.19710239999998</v>
+        <v>47.68283729999998</v>
       </c>
       <c r="P78">
-        <v>144.5913071999999</v>
+        <v>143.0485118999999</v>
       </c>
       <c r="Q78">
-        <v>156.5913071999999</v>
+        <v>155.0485118999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2300474237225339</v>
+        <v>0.2374647918273058</v>
       </c>
       <c r="T78">
-        <v>2.850249047285101</v>
+        <v>2.964993372860185</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.233162429260705</v>
+        <v>2.204160319789787</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09839140212028034</v>
+        <v>0.09836542254715253</v>
       </c>
       <c r="C79">
-        <v>532.2422485998181</v>
+        <v>506.3130777111701</v>
       </c>
       <c r="D79">
-        <v>2445.868248599818</v>
+        <v>2447.07707771117</v>
       </c>
       <c r="E79">
-        <v>352.0260000000003</v>
+        <v>379.1640000000002</v>
       </c>
       <c r="F79">
-        <v>2089.626</v>
+        <v>2116.764</v>
       </c>
       <c r="G79">
         <v>176</v>
@@ -7765,28 +7765,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M79">
-        <v>158.3936508</v>
+        <v>160.4507112</v>
       </c>
       <c r="N79">
-        <v>190.7313491999999</v>
+        <v>188.6742887999999</v>
       </c>
       <c r="O79">
-        <v>47.68283729999998</v>
+        <v>47.16857219999998</v>
       </c>
       <c r="P79">
-        <v>143.0485118999999</v>
+        <v>141.5057165999999</v>
       </c>
       <c r="Q79">
-        <v>155.0485118999999</v>
+        <v>153.5057165999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2374647918273058</v>
+        <v>0.2455564661234206</v>
       </c>
       <c r="T79">
-        <v>2.964993372860185</v>
+        <v>3.090169000760277</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.204160319789787</v>
+        <v>2.175901854151457</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09836542254715253</v>
+        <v>0.09833944297402475</v>
       </c>
       <c r="C80">
-        <v>506.3130777111701</v>
+        <v>480.3851023001466</v>
       </c>
       <c r="D80">
-        <v>2447.07707771117</v>
+        <v>2448.287102300147</v>
       </c>
       <c r="E80">
-        <v>379.1640000000002</v>
+        <v>406.3020000000001</v>
       </c>
       <c r="F80">
-        <v>2116.764</v>
+        <v>2143.902</v>
       </c>
       <c r="G80">
         <v>176</v>
@@ -7847,28 +7847,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M80">
-        <v>160.4507112</v>
+        <v>162.5077716</v>
       </c>
       <c r="N80">
-        <v>188.6742887999999</v>
+        <v>186.6172283999999</v>
       </c>
       <c r="O80">
-        <v>47.16857219999998</v>
+        <v>46.65430709999998</v>
       </c>
       <c r="P80">
-        <v>141.5057165999999</v>
+        <v>139.9629212999999</v>
       </c>
       <c r="Q80">
-        <v>153.5057165999999</v>
+        <v>151.9629212999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2455564661234206</v>
+        <v>0.2544187760667845</v>
       </c>
       <c r="T80">
-        <v>3.090169000760277</v>
+        <v>3.227266117031808</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.175901854151457</v>
+        <v>2.148358792706502</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09833944297402475</v>
+        <v>0.09831346340089692</v>
       </c>
       <c r="C81">
-        <v>480.3851023001466</v>
+        <v>454.4583241410401</v>
       </c>
       <c r="D81">
-        <v>2448.287102300147</v>
+        <v>2449.49832414104</v>
       </c>
       <c r="E81">
-        <v>406.3020000000001</v>
+        <v>433.4400000000005</v>
       </c>
       <c r="F81">
-        <v>2143.902</v>
+        <v>2171.04</v>
       </c>
       <c r="G81">
         <v>176</v>
@@ -7929,28 +7929,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M81">
-        <v>162.5077716</v>
+        <v>164.5648320000001</v>
       </c>
       <c r="N81">
-        <v>186.6172283999999</v>
+        <v>184.5601679999999</v>
       </c>
       <c r="O81">
-        <v>46.65430709999998</v>
+        <v>46.14004199999997</v>
       </c>
       <c r="P81">
-        <v>139.9629212999999</v>
+        <v>138.4201259999999</v>
       </c>
       <c r="Q81">
-        <v>151.9629212999999</v>
+        <v>150.4201259999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2544187760667845</v>
+        <v>0.2641673170044846</v>
       </c>
       <c r="T81">
-        <v>3.227266117031808</v>
+        <v>3.37807294493049</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.148358792706502</v>
+        <v>2.12150430779767</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09831346340089692</v>
+        <v>0.09828748382776911</v>
       </c>
       <c r="C82">
-        <v>454.4583241410401</v>
+        <v>428.5327450116474</v>
       </c>
       <c r="D82">
-        <v>2449.49832414104</v>
+        <v>2450.710745011648</v>
       </c>
       <c r="E82">
-        <v>433.4400000000005</v>
+        <v>460.5780000000004</v>
       </c>
       <c r="F82">
-        <v>2171.04</v>
+        <v>2198.178</v>
       </c>
       <c r="G82">
         <v>176</v>
@@ -8011,28 +8011,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M82">
-        <v>164.5648320000001</v>
+        <v>166.6218924</v>
       </c>
       <c r="N82">
-        <v>184.5601679999999</v>
+        <v>182.5031075999999</v>
       </c>
       <c r="O82">
-        <v>46.14004199999997</v>
+        <v>45.62577689999998</v>
       </c>
       <c r="P82">
-        <v>138.4201259999999</v>
+        <v>136.8773306999999</v>
       </c>
       <c r="Q82">
-        <v>150.4201259999999</v>
+        <v>148.8773306999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2641673170044846</v>
+        <v>0.2749420201461533</v>
       </c>
       <c r="T82">
-        <v>3.37807294493049</v>
+        <v>3.544754175765876</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.12150430779767</v>
+        <v>2.095312896590292</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09828748382776911</v>
+        <v>0.09826150425464131</v>
       </c>
       <c r="C83">
-        <v>428.5327450116474</v>
+        <v>402.6083666932923</v>
       </c>
       <c r="D83">
-        <v>2450.710745011648</v>
+        <v>2451.924366693293</v>
       </c>
       <c r="E83">
-        <v>460.5780000000004</v>
+        <v>487.7160000000003</v>
       </c>
       <c r="F83">
-        <v>2198.178</v>
+        <v>2225.316</v>
       </c>
       <c r="G83">
         <v>176</v>
@@ -8093,28 +8093,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M83">
-        <v>166.6218924</v>
+        <v>168.6789528</v>
       </c>
       <c r="N83">
-        <v>182.5031075999999</v>
+        <v>180.4460471999999</v>
       </c>
       <c r="O83">
-        <v>45.62577689999998</v>
+        <v>45.11151179999997</v>
       </c>
       <c r="P83">
-        <v>136.8773306999999</v>
+        <v>135.3345353999999</v>
       </c>
       <c r="Q83">
-        <v>148.8773306999999</v>
+        <v>147.3345353999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2749420201461533</v>
+        <v>0.2869139125257851</v>
       </c>
       <c r="T83">
-        <v>3.544754175765876</v>
+        <v>3.72995554336075</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.095312896590292</v>
+        <v>2.06976030029041</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09826150425464131</v>
+        <v>0.09823552468151352</v>
       </c>
       <c r="C84">
-        <v>402.6083666932923</v>
+        <v>376.6851909708262</v>
       </c>
       <c r="D84">
-        <v>2451.924366693293</v>
+        <v>2453.139190970826</v>
       </c>
       <c r="E84">
-        <v>487.7160000000003</v>
+        <v>514.8540000000003</v>
       </c>
       <c r="F84">
-        <v>2225.316</v>
+        <v>2252.454</v>
       </c>
       <c r="G84">
         <v>176</v>
@@ -8175,28 +8175,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M84">
-        <v>168.6789528</v>
+        <v>170.7360132</v>
       </c>
       <c r="N84">
-        <v>180.4460471999999</v>
+        <v>178.3889867999999</v>
       </c>
       <c r="O84">
-        <v>45.11151179999997</v>
+        <v>44.59724669999998</v>
       </c>
       <c r="P84">
-        <v>135.3345353999999</v>
+        <v>133.7917400999999</v>
       </c>
       <c r="Q84">
-        <v>147.3345353999999</v>
+        <v>145.7917400999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2869139125257851</v>
+        <v>0.3002942628324325</v>
       </c>
       <c r="T84">
-        <v>3.72995554336075</v>
+        <v>3.936945307143256</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.06976030029041</v>
+        <v>2.044823429202574</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09823552468151352</v>
+        <v>0.09820954510838573</v>
       </c>
       <c r="C85">
-        <v>376.6851909708262</v>
+        <v>350.7632196326408</v>
       </c>
       <c r="D85">
-        <v>2453.139190970826</v>
+        <v>2454.355219632641</v>
       </c>
       <c r="E85">
-        <v>514.8540000000003</v>
+        <v>541.9920000000006</v>
       </c>
       <c r="F85">
-        <v>2252.454</v>
+        <v>2279.592000000001</v>
       </c>
       <c r="G85">
         <v>176</v>
@@ -8257,28 +8257,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M85">
-        <v>170.7360132</v>
+        <v>172.7930736</v>
       </c>
       <c r="N85">
-        <v>178.3889867999999</v>
+        <v>176.3319263999999</v>
       </c>
       <c r="O85">
-        <v>44.59724669999998</v>
+        <v>44.08298159999998</v>
       </c>
       <c r="P85">
-        <v>133.7917400999999</v>
+        <v>132.2489447999999</v>
       </c>
       <c r="Q85">
-        <v>145.7917400999999</v>
+        <v>144.2489447999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3002942628324325</v>
+        <v>0.3153471569274108</v>
       </c>
       <c r="T85">
-        <v>3.936945307143256</v>
+        <v>4.169808791398575</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.044823429202574</v>
+        <v>2.020480293140638</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09820954510838573</v>
+        <v>0.1072360655352579</v>
       </c>
       <c r="C86">
-        <v>350.7632196326413</v>
+        <v>-36.98197960442894</v>
       </c>
       <c r="D86">
-        <v>2454.355219632641</v>
+        <v>2093.748020395571</v>
       </c>
       <c r="E86">
-        <v>541.9920000000002</v>
+        <v>569.1300000000001</v>
       </c>
       <c r="F86">
-        <v>2279.592</v>
+        <v>2306.73</v>
       </c>
       <c r="G86">
         <v>176</v>
@@ -8339,45 +8339,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M86">
-        <v>172.7930736</v>
+        <v>207.6057</v>
       </c>
       <c r="N86">
-        <v>176.3319263999999</v>
+        <v>141.5193</v>
       </c>
       <c r="O86">
-        <v>44.08298159999998</v>
+        <v>35.37982499999999</v>
       </c>
       <c r="P86">
-        <v>132.2489447999999</v>
+        <v>106.139475</v>
       </c>
       <c r="Q86">
-        <v>144.2489447999999</v>
+        <v>118.139475</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3153471569274107</v>
+        <v>0.3324071035683861</v>
       </c>
       <c r="T86">
-        <v>4.169808791398572</v>
+        <v>4.433720740221267</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.020480293140638</v>
+        <v>1.681673480063409</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1072360655352579</v>
+        <v>0.1073165859621301</v>
       </c>
       <c r="C87">
-        <v>-36.98197960442894</v>
+        <v>-66.86053293209307</v>
       </c>
       <c r="D87">
-        <v>2093.748020395571</v>
+        <v>2091.007467067907</v>
       </c>
       <c r="E87">
-        <v>569.1300000000001</v>
+        <v>596.268</v>
       </c>
       <c r="F87">
-        <v>2306.73</v>
+        <v>2333.868</v>
       </c>
       <c r="G87">
         <v>176</v>
@@ -8421,28 +8421,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M87">
-        <v>207.6057</v>
+        <v>210.04812</v>
       </c>
       <c r="N87">
-        <v>141.5193</v>
+        <v>139.07688</v>
       </c>
       <c r="O87">
-        <v>35.37982499999999</v>
+        <v>34.76921999999999</v>
       </c>
       <c r="P87">
-        <v>106.139475</v>
+        <v>104.30766</v>
       </c>
       <c r="Q87">
-        <v>118.139475</v>
+        <v>116.30766</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3324071035683861</v>
+        <v>0.3519041854437864</v>
       </c>
       <c r="T87">
-        <v>4.433720740221267</v>
+        <v>4.735334396018632</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.681673480063409</v>
+        <v>1.662119137271973</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1073165859621301</v>
+        <v>0.1073971063890023</v>
       </c>
       <c r="C88">
-        <v>-66.86053293209307</v>
+        <v>-96.73192129579184</v>
       </c>
       <c r="D88">
-        <v>2091.007467067907</v>
+        <v>2088.274078704208</v>
       </c>
       <c r="E88">
-        <v>596.268</v>
+        <v>623.4060000000004</v>
       </c>
       <c r="F88">
-        <v>2333.868</v>
+        <v>2361.006</v>
       </c>
       <c r="G88">
         <v>176</v>
@@ -8503,28 +8503,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M88">
-        <v>210.04812</v>
+        <v>212.49054</v>
       </c>
       <c r="N88">
-        <v>139.07688</v>
+        <v>136.6344599999999</v>
       </c>
       <c r="O88">
-        <v>34.76921999999999</v>
+        <v>34.15861499999998</v>
       </c>
       <c r="P88">
-        <v>104.30766</v>
+        <v>102.4758449999999</v>
       </c>
       <c r="Q88">
-        <v>116.30766</v>
+        <v>114.4758449999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3519041854437864</v>
+        <v>0.3744008183769407</v>
       </c>
       <c r="T88">
-        <v>4.735334396018632</v>
+        <v>5.083350152707899</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.662119137271973</v>
+        <v>1.643014319602181</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1073971063890023</v>
+        <v>0.1074776268158745</v>
       </c>
       <c r="C89">
-        <v>-96.73192129579184</v>
+        <v>-126.5961727572076</v>
       </c>
       <c r="D89">
-        <v>2088.274078704208</v>
+        <v>2085.547827242793</v>
       </c>
       <c r="E89">
-        <v>623.4060000000004</v>
+        <v>650.5440000000003</v>
       </c>
       <c r="F89">
-        <v>2361.006</v>
+        <v>2388.144</v>
       </c>
       <c r="G89">
         <v>176</v>
@@ -8585,28 +8585,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M89">
-        <v>212.49054</v>
+        <v>214.93296</v>
       </c>
       <c r="N89">
-        <v>136.6344599999999</v>
+        <v>134.1920399999999</v>
       </c>
       <c r="O89">
-        <v>34.15861499999998</v>
+        <v>33.54800999999998</v>
       </c>
       <c r="P89">
-        <v>102.4758449999999</v>
+        <v>100.64403</v>
       </c>
       <c r="Q89">
-        <v>114.4758449999999</v>
+        <v>112.64403</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3744008183769407</v>
+        <v>0.4006468901322875</v>
       </c>
       <c r="T89">
-        <v>5.083350152707899</v>
+        <v>5.489368535512045</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.643014319602181</v>
+        <v>1.624343702333974</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1074776268158745</v>
+        <v>0.1075581472427467</v>
       </c>
       <c r="C90">
-        <v>-126.5961727572076</v>
+        <v>-156.4533152316721</v>
       </c>
       <c r="D90">
-        <v>2085.547827242793</v>
+        <v>2082.828684768328</v>
       </c>
       <c r="E90">
-        <v>650.5440000000003</v>
+        <v>677.6820000000002</v>
       </c>
       <c r="F90">
-        <v>2388.144</v>
+        <v>2415.282</v>
       </c>
       <c r="G90">
         <v>176</v>
@@ -8667,28 +8667,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M90">
-        <v>214.93296</v>
+        <v>217.37538</v>
       </c>
       <c r="N90">
-        <v>134.1920399999999</v>
+        <v>131.7496199999999</v>
       </c>
       <c r="O90">
-        <v>33.54800999999998</v>
+        <v>32.93740499999998</v>
       </c>
       <c r="P90">
-        <v>100.64403</v>
+        <v>98.81221499999995</v>
       </c>
       <c r="Q90">
-        <v>112.64403</v>
+        <v>110.812215</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4006468901322875</v>
+        <v>0.4316649749340609</v>
       </c>
       <c r="T90">
-        <v>5.489368535512045</v>
+        <v>5.969208442462399</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.624343702333974</v>
+        <v>1.606092649498761</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1075581472427467</v>
+        <v>0.1076386676696189</v>
       </c>
       <c r="C91">
-        <v>-156.4533152316721</v>
+        <v>-186.3033764891243</v>
       </c>
       <c r="D91">
-        <v>2082.828684768328</v>
+        <v>2080.116623510876</v>
       </c>
       <c r="E91">
-        <v>677.6820000000002</v>
+        <v>704.8200000000002</v>
       </c>
       <c r="F91">
-        <v>2415.282</v>
+        <v>2442.42</v>
       </c>
       <c r="G91">
         <v>176</v>
@@ -8749,28 +8749,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M91">
-        <v>217.37538</v>
+        <v>219.8178</v>
       </c>
       <c r="N91">
-        <v>131.7496199999999</v>
+        <v>129.3071999999999</v>
       </c>
       <c r="O91">
-        <v>32.93740499999998</v>
+        <v>32.32679999999998</v>
       </c>
       <c r="P91">
-        <v>98.81221499999995</v>
+        <v>96.98039999999995</v>
       </c>
       <c r="Q91">
-        <v>110.812215</v>
+        <v>108.9803999999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4316649749340609</v>
+        <v>0.4688866766961891</v>
       </c>
       <c r="T91">
-        <v>5.969208442462399</v>
+        <v>6.545016330802825</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.606092649498761</v>
+        <v>1.588247175615441</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1076386676696189</v>
+        <v>0.1077191880964911</v>
       </c>
       <c r="C92">
-        <v>-186.3033764891243</v>
+        <v>-216.1463841550517</v>
       </c>
       <c r="D92">
-        <v>2080.116623510876</v>
+        <v>2077.411615844949</v>
       </c>
       <c r="E92">
-        <v>704.8200000000002</v>
+        <v>731.9580000000005</v>
       </c>
       <c r="F92">
-        <v>2442.42</v>
+        <v>2469.558</v>
       </c>
       <c r="G92">
         <v>176</v>
@@ -8831,28 +8831,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M92">
-        <v>219.8178</v>
+        <v>222.26022</v>
       </c>
       <c r="N92">
-        <v>129.3071999999999</v>
+        <v>126.8647799999999</v>
       </c>
       <c r="O92">
-        <v>32.32679999999998</v>
+        <v>31.71619499999998</v>
       </c>
       <c r="P92">
-        <v>96.98039999999995</v>
+        <v>95.14858499999994</v>
       </c>
       <c r="Q92">
-        <v>108.9803999999999</v>
+        <v>107.1485849999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4688866766961891</v>
+        <v>0.51437986773879</v>
       </c>
       <c r="T92">
-        <v>6.545016330802825</v>
+        <v>7.248781527663343</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.588247175615441</v>
+        <v>1.570793909949337</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1077191880964911</v>
+        <v>0.1077997085233633</v>
       </c>
       <c r="C93">
-        <v>-216.1463841550517</v>
+        <v>-245.9823657114343</v>
       </c>
       <c r="D93">
-        <v>2077.411615844949</v>
+        <v>2074.713634288566</v>
       </c>
       <c r="E93">
-        <v>731.9580000000005</v>
+        <v>759.0960000000005</v>
       </c>
       <c r="F93">
-        <v>2469.558</v>
+        <v>2496.696</v>
       </c>
       <c r="G93">
         <v>176</v>
@@ -8913,28 +8913,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M93">
-        <v>222.26022</v>
+        <v>224.70264</v>
       </c>
       <c r="N93">
-        <v>126.8647799999999</v>
+        <v>124.4223599999999</v>
       </c>
       <c r="O93">
-        <v>31.71619499999998</v>
+        <v>31.10558999999998</v>
       </c>
       <c r="P93">
-        <v>95.14858499999994</v>
+        <v>93.31676999999993</v>
       </c>
       <c r="Q93">
-        <v>107.1485849999999</v>
+        <v>105.3167699999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.51437986773879</v>
+        <v>0.5712463565420413</v>
       </c>
       <c r="T93">
-        <v>7.248781527663343</v>
+        <v>8.128488023738994</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.570793909949337</v>
+        <v>1.553720063102062</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1077997085233633</v>
+        <v>0.1078802289502355</v>
       </c>
       <c r="C94">
-        <v>-245.9823657114343</v>
+        <v>-275.811348497667</v>
       </c>
       <c r="D94">
-        <v>2074.713634288566</v>
+        <v>2072.022651502333</v>
       </c>
       <c r="E94">
-        <v>759.0960000000005</v>
+        <v>786.2340000000004</v>
       </c>
       <c r="F94">
-        <v>2496.696</v>
+        <v>2523.834</v>
       </c>
       <c r="G94">
         <v>176</v>
@@ -8995,28 +8995,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M94">
-        <v>224.70264</v>
+        <v>227.14506</v>
       </c>
       <c r="N94">
-        <v>124.4223599999999</v>
+        <v>121.9799399999999</v>
       </c>
       <c r="O94">
-        <v>31.10558999999998</v>
+        <v>30.49498499999998</v>
       </c>
       <c r="P94">
-        <v>93.31676999999993</v>
+        <v>91.48495499999993</v>
       </c>
       <c r="Q94">
-        <v>105.3167699999999</v>
+        <v>103.4849549999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5712463565420413</v>
+        <v>0.644360413574793</v>
       </c>
       <c r="T94">
-        <v>8.128488023738994</v>
+        <v>9.259539232979115</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.553720063102062</v>
+        <v>1.537013395756878</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1078802289502355</v>
+        <v>0.1079607493771077</v>
       </c>
       <c r="C95">
-        <v>-275.811348497667</v>
+        <v>-305.6333597114899</v>
       </c>
       <c r="D95">
-        <v>2072.022651502333</v>
+        <v>2069.33864028851</v>
       </c>
       <c r="E95">
-        <v>786.2340000000004</v>
+        <v>813.3720000000003</v>
       </c>
       <c r="F95">
-        <v>2523.834</v>
+        <v>2550.972</v>
       </c>
       <c r="G95">
         <v>176</v>
@@ -9077,28 +9077,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M95">
-        <v>227.14506</v>
+        <v>229.58748</v>
       </c>
       <c r="N95">
-        <v>121.9799399999999</v>
+        <v>119.5375199999999</v>
       </c>
       <c r="O95">
-        <v>30.49498499999998</v>
+        <v>29.88437999999999</v>
       </c>
       <c r="P95">
-        <v>91.48495499999993</v>
+        <v>89.65313999999995</v>
       </c>
       <c r="Q95">
-        <v>103.4849549999999</v>
+        <v>101.65314</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.644360413574793</v>
+        <v>0.7418458229517952</v>
       </c>
       <c r="T95">
-        <v>9.259539232979115</v>
+        <v>10.76760751196594</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.537013395756878</v>
+        <v>1.52066218941904</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1079607493771077</v>
+        <v>0.1080412698039799</v>
       </c>
       <c r="C96">
-        <v>-305.6333597114899</v>
+        <v>-335.4484264099037</v>
       </c>
       <c r="D96">
-        <v>2069.33864028851</v>
+        <v>2066.661573590096</v>
       </c>
       <c r="E96">
-        <v>813.3720000000003</v>
+        <v>840.5100000000002</v>
       </c>
       <c r="F96">
-        <v>2550.972</v>
+        <v>2578.11</v>
       </c>
       <c r="G96">
         <v>176</v>
@@ -9159,28 +9159,28 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M96">
-        <v>229.58748</v>
+        <v>232.0299</v>
       </c>
       <c r="N96">
-        <v>119.5375199999999</v>
+        <v>117.0950999999999</v>
       </c>
       <c r="O96">
-        <v>29.88437999999999</v>
+        <v>29.27377499999999</v>
       </c>
       <c r="P96">
-        <v>89.65313999999995</v>
+        <v>87.82132499999996</v>
       </c>
       <c r="Q96">
-        <v>101.65314</v>
+        <v>99.82132499999996</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7418458229517952</v>
+        <v>0.8783253960795988</v>
       </c>
       <c r="T96">
-        <v>10.76760751196594</v>
+        <v>12.87890310254751</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.52066218941904</v>
+        <v>1.504655219004102</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1080412698039799</v>
+        <v>0.1532294513151373</v>
       </c>
       <c r="C97">
-        <v>-335.4484264099037</v>
+        <v>-1231.888811987336</v>
       </c>
       <c r="D97">
-        <v>2066.661573590096</v>
+        <v>1197.359188012665</v>
       </c>
       <c r="E97">
-        <v>840.5100000000002</v>
+        <v>867.6480000000006</v>
       </c>
       <c r="F97">
-        <v>2578.11</v>
+        <v>2605.248000000001</v>
       </c>
       <c r="G97">
         <v>176</v>
@@ -9241,45 +9241,45 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M97">
-        <v>232.0299</v>
+        <v>382.4504064000001</v>
       </c>
       <c r="N97">
-        <v>117.0950999999999</v>
+        <v>-33.32540640000019</v>
       </c>
       <c r="O97">
-        <v>29.27377499999999</v>
+        <v>-8.331351600000048</v>
       </c>
       <c r="P97">
-        <v>87.82132499999996</v>
+        <v>-24.99405480000014</v>
       </c>
       <c r="Q97">
-        <v>99.82132499999996</v>
+        <v>-12.99405480000014</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8783253960795988</v>
+        <v>1.11158641553375</v>
       </c>
       <c r="T97">
-        <v>12.87890310254751</v>
+        <v>16.48737688760936</v>
       </c>
       <c r="U97">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.25</v>
+        <v>0.2282158641732848</v>
       </c>
       <c r="W97">
-        <v>0.0675</v>
+        <v>0.1132979111393618</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.504655219004102</v>
+        <v>0.9128634566931391</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1532294513151373</v>
+        <v>0.1542394513151373</v>
       </c>
       <c r="C98">
-        <v>-1231.888811987335</v>
+        <v>-1270.178959708725</v>
       </c>
       <c r="D98">
-        <v>1197.359188012665</v>
+        <v>1186.207040291275</v>
       </c>
       <c r="E98">
-        <v>867.6480000000001</v>
+        <v>894.7860000000001</v>
       </c>
       <c r="F98">
-        <v>2605.248</v>
+        <v>2632.386</v>
       </c>
       <c r="G98">
         <v>176</v>
@@ -9323,37 +9323,37 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M98">
-        <v>382.4504064</v>
+        <v>386.4342648000001</v>
       </c>
       <c r="N98">
-        <v>-33.32540640000008</v>
+        <v>-37.30926480000011</v>
       </c>
       <c r="O98">
-        <v>-8.331351600000019</v>
+        <v>-9.327316200000027</v>
       </c>
       <c r="P98">
-        <v>-24.99405480000006</v>
+        <v>-27.98194860000008</v>
       </c>
       <c r="Q98">
-        <v>-12.99405480000006</v>
+        <v>-15.98194860000008</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.111586415533748</v>
+        <v>1.466848554044997</v>
       </c>
       <c r="T98">
-        <v>16.48737688760932</v>
+        <v>21.98316918347909</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2282158641732848</v>
+        <v>0.225863123305519</v>
       </c>
       <c r="W98">
-        <v>0.1132979111393618</v>
+        <v>0.1136432934987498</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9128634566931393</v>
+        <v>0.903452493222076</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1542394513151373</v>
+        <v>0.1552494513151372</v>
       </c>
       <c r="C99">
-        <v>-1270.178959708725</v>
+        <v>-1308.263283297361</v>
       </c>
       <c r="D99">
-        <v>1186.207040291275</v>
+        <v>1175.26071670264</v>
       </c>
       <c r="E99">
-        <v>894.7860000000001</v>
+        <v>921.9240000000004</v>
       </c>
       <c r="F99">
-        <v>2632.386</v>
+        <v>2659.524</v>
       </c>
       <c r="G99">
         <v>176</v>
@@ -9405,37 +9405,37 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M99">
-        <v>386.4342648000001</v>
+        <v>390.4181232000001</v>
       </c>
       <c r="N99">
-        <v>-37.30926480000011</v>
+        <v>-41.29312320000014</v>
       </c>
       <c r="O99">
-        <v>-9.327316200000027</v>
+        <v>-10.32328080000003</v>
       </c>
       <c r="P99">
-        <v>-27.98194860000008</v>
+        <v>-30.9698424000001</v>
       </c>
       <c r="Q99">
-        <v>-15.98194860000008</v>
+        <v>-18.9698424000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.466848554044997</v>
+        <v>2.177372831067494</v>
       </c>
       <c r="T99">
-        <v>21.98316918347909</v>
+        <v>32.97475377521863</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.225863123305519</v>
+        <v>0.2235583975575035</v>
       </c>
       <c r="W99">
-        <v>0.1136432934987498</v>
+        <v>0.1139816272385585</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.903452493222076</v>
+        <v>0.8942335902300138</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1552494513151372</v>
+        <v>0.1562594513151372</v>
       </c>
       <c r="C100">
-        <v>-1308.263283297361</v>
+        <v>-1346.147428690417</v>
       </c>
       <c r="D100">
-        <v>1175.26071670264</v>
+        <v>1164.514571309584</v>
       </c>
       <c r="E100">
-        <v>921.9240000000004</v>
+        <v>949.0620000000004</v>
       </c>
       <c r="F100">
-        <v>2659.524</v>
+        <v>2686.662</v>
       </c>
       <c r="G100">
         <v>176</v>
@@ -9487,37 +9487,37 @@
         <v>349.1249999999999</v>
       </c>
       <c r="M100">
-        <v>390.4181232000001</v>
+        <v>394.4019816000001</v>
       </c>
       <c r="N100">
-        <v>-41.29312320000014</v>
+        <v>-45.27698160000011</v>
       </c>
       <c r="O100">
-        <v>-10.32328080000003</v>
+        <v>-11.31924540000003</v>
       </c>
       <c r="P100">
-        <v>-30.9698424000001</v>
+        <v>-33.95773620000008</v>
       </c>
       <c r="Q100">
-        <v>-18.9698424000001</v>
+        <v>-21.95773620000008</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.177372831067494</v>
+        <v>4.308945662134989</v>
       </c>
       <c r="T100">
-        <v>32.97475377521863</v>
+        <v>65.94950755043726</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2235583975575035</v>
+        <v>0.2213002319256095</v>
       </c>
       <c r="W100">
-        <v>0.1139816272385585</v>
+        <v>0.1143131259533205</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8942335902300138</v>
+        <v>0.885200927702438</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1562594513151372</v>
-      </c>
-      <c r="C101">
-        <v>-1346.147428690417</v>
-      </c>
-      <c r="D101">
-        <v>1164.514571309584</v>
-      </c>
-      <c r="E101">
-        <v>949.0620000000004</v>
-      </c>
-      <c r="F101">
-        <v>2686.662</v>
-      </c>
-      <c r="G101">
-        <v>176</v>
-      </c>
-      <c r="H101">
-        <v>976.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>361.1249999999999</v>
-      </c>
-      <c r="K101">
-        <v>12</v>
-      </c>
-      <c r="L101">
-        <v>349.1249999999999</v>
-      </c>
-      <c r="M101">
-        <v>394.4019816000001</v>
-      </c>
-      <c r="N101">
-        <v>-45.27698160000011</v>
-      </c>
-      <c r="O101">
-        <v>-11.31924540000003</v>
-      </c>
-      <c r="P101">
-        <v>-33.95773620000008</v>
-      </c>
-      <c r="Q101">
-        <v>-21.95773620000008</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.308945662134989</v>
-      </c>
-      <c r="T101">
-        <v>65.94950755043726</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2213002319256095</v>
-      </c>
-      <c r="W101">
-        <v>0.1143131259533205</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.885200927702438</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
